--- a/(WORK) 工作/Projects_HAESL/proj_digital_streamer/assets/2026-04-21 Streamer feedback review (issue category)/file-20260421110907797.xlsx
+++ b/(WORK) 工作/Projects_HAESL/proj_digital_streamer/assets/2026-04-21 Streamer feedback review (issue category)/file-20260421110907797.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yk-chris.chan\Documents\GitHub\Obsidian_2nd_brain\(WORK) 工作\Projects_HAESL\proj_digital_streamer\assets\2026-04-21 Streamer feedback review (issue category)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4761E83-6C4D-46BD-9B51-35822CACE6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7D0E72-D173-4ED1-A64A-55092FF00D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{576FD22E-F0EC-42CA-9339-4ABADA5B6AB9}"/>
   </bookViews>
@@ -1573,9 +1573,6 @@
     <t>On Notification, there are two area for notifying the task owners. Firstly, it is general message notfiication from the task actions like changing the task date from different planner or task owners. Another notification type is to notify the line manager as a supper task owner to accept or reject the approval requests from the staff under the same department group.</t>
   </si>
   <si>
-    <t>In specific streamer arrangement, the template with the label of DIW/Cost Review. Once the status of the active streamer is under the status of DIW/Cost Review, the planner would release the investigation or quotation after the first induction. Therefore, the planner is able to re-input the second induction information later on.</t>
-  </si>
-  <si>
     <t>Comments (Consolidated)</t>
   </si>
   <si>
@@ -1604,6 +1601,9 @@
   </si>
   <si>
     <t>low</t>
+  </si>
+  <si>
+    <t>In specific streamer arrangement, the template with the label of DIW/Cost Review can be selected. Once the status of the active streamer is under the status of DIW/Cost Review, the planner would release the investigation or quotation after all tasks are completed in the first induction. Therefore, the planner is able to re-input the second induction information later on.</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1920,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2108,60 +2108,60 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2171,6 +2171,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2673,69 +2676,69 @@
       <c r="A3" s="68">
         <v>2</v>
       </c>
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="69" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="69">
+      <c r="G3" s="70">
         <v>46097</v>
       </c>
       <c r="H3" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="66" t="s">
+      <c r="I3" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="66" t="s">
+      <c r="J3" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="66" t="s">
+      <c r="K3" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="65"/>
-      <c r="M3" s="67" t="s">
+      <c r="M3" s="66" t="s">
         <v>32</v>
       </c>
       <c r="N3" s="65"/>
-      <c r="O3" s="67" t="s">
+      <c r="O3" s="66" t="s">
         <v>26</v>
       </c>
       <c r="P3" s="65"/>
-      <c r="Q3" s="71" t="s">
+      <c r="Q3" s="67" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="68"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
       <c r="F4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="69"/>
+      <c r="G4" s="70"/>
       <c r="H4" s="68"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
       <c r="L4" s="65"/>
-      <c r="M4" s="67"/>
+      <c r="M4" s="66"/>
       <c r="N4" s="65"/>
-      <c r="O4" s="67"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="65"/>
-      <c r="Q4" s="71"/>
+      <c r="Q4" s="67"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="14">
@@ -3195,36 +3198,36 @@
       <c r="A15" s="68">
         <v>13</v>
       </c>
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="66" t="s">
+      <c r="D15" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="66" t="s">
+      <c r="E15" s="69" t="s">
         <v>20</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="70">
         <v>46097</v>
       </c>
       <c r="H15" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="I15" s="66" t="s">
+      <c r="I15" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J15" s="66" t="s">
+      <c r="J15" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="66"/>
+      <c r="K15" s="69"/>
       <c r="L15" s="65"/>
-      <c r="M15" s="66" t="s">
+      <c r="M15" s="69" t="s">
         <v>78</v>
       </c>
       <c r="N15" s="65"/>
@@ -3238,20 +3241,20 @@
     </row>
     <row r="16" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" s="68"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
       <c r="F16" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="69"/>
+      <c r="G16" s="70"/>
       <c r="H16" s="68"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="66"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
       <c r="L16" s="65"/>
-      <c r="M16" s="66"/>
+      <c r="M16" s="69"/>
       <c r="N16" s="65"/>
       <c r="O16" s="65"/>
       <c r="P16" s="65"/>
@@ -3259,20 +3262,20 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="68"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
       <c r="F17" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="69"/>
+      <c r="G17" s="70"/>
       <c r="H17" s="68"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
       <c r="L17" s="65"/>
-      <c r="M17" s="66"/>
+      <c r="M17" s="69"/>
       <c r="N17" s="65"/>
       <c r="O17" s="65"/>
       <c r="P17" s="65"/>
@@ -3282,39 +3285,39 @@
       <c r="A18" s="68">
         <v>14</v>
       </c>
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="66" t="s">
+      <c r="D18" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="69" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="69">
+      <c r="G18" s="70">
         <v>46097</v>
       </c>
       <c r="H18" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="I18" s="66" t="s">
+      <c r="I18" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J18" s="66" t="s">
+      <c r="J18" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="66"/>
+      <c r="K18" s="69"/>
       <c r="L18" s="65"/>
-      <c r="M18" s="66" t="s">
+      <c r="M18" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="N18" s="66"/>
+      <c r="N18" s="69"/>
       <c r="O18" s="65" t="s">
         <v>80</v>
       </c>
@@ -3325,42 +3328,42 @@
     </row>
     <row r="19" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" s="68"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
       <c r="F19" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="69"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="68"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
       <c r="L19" s="65"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="69"/>
       <c r="O19" s="65"/>
       <c r="P19" s="65"/>
       <c r="Q19" s="65"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20" s="68"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
       <c r="F20" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="69"/>
+      <c r="G20" s="70"/>
       <c r="H20" s="68"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
       <c r="L20" s="65"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="69"/>
       <c r="O20" s="65"/>
       <c r="P20" s="65"/>
       <c r="Q20" s="65"/>
@@ -3553,41 +3556,41 @@
       <c r="A25" s="68">
         <v>19</v>
       </c>
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="67" t="s">
+      <c r="E25" s="66" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G25" s="69">
+      <c r="G25" s="70">
         <v>46098</v>
       </c>
-      <c r="H25" s="70" t="s">
+      <c r="H25" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="66" t="s">
+      <c r="I25" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J25" s="66" t="s">
+      <c r="J25" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="66" t="s">
+      <c r="K25" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L25" s="65"/>
-      <c r="M25" s="67" t="s">
+      <c r="M25" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="N25" s="66"/>
+      <c r="N25" s="69"/>
       <c r="O25" s="65" t="s">
         <v>85</v>
       </c>
@@ -3598,21 +3601,21 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26" s="68"/>
-      <c r="B26" s="66"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
       <c r="F26" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G26" s="69"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
       <c r="L26" s="65"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="66"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="69"/>
       <c r="O26" s="65"/>
       <c r="P26" s="65"/>
       <c r="Q26" s="65"/>
@@ -4131,38 +4134,38 @@
       <c r="B38" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C38" s="67" t="s">
+      <c r="C38" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="67" t="s">
+      <c r="D38" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="67" t="s">
+      <c r="E38" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="84" t="s">
+      <c r="F38" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="G38" s="69">
+      <c r="G38" s="70">
         <v>46099</v>
       </c>
-      <c r="H38" s="70" t="s">
+      <c r="H38" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="66" t="s">
+      <c r="I38" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J38" s="66" t="s">
+      <c r="J38" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K38" s="66" t="s">
+      <c r="K38" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L38" s="65"/>
-      <c r="M38" s="67" t="s">
+      <c r="M38" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="N38" s="66"/>
+      <c r="N38" s="69"/>
       <c r="O38" s="65" t="s">
         <v>111</v>
       </c>
@@ -4176,18 +4179,18 @@
       <c r="B39" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="66"/>
-      <c r="J39" s="66"/>
-      <c r="K39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
       <c r="L39" s="65"/>
-      <c r="M39" s="67"/>
-      <c r="N39" s="66"/>
+      <c r="M39" s="66"/>
+      <c r="N39" s="69"/>
       <c r="O39" s="65"/>
       <c r="P39" s="65"/>
       <c r="Q39" s="65"/>
@@ -4384,39 +4387,39 @@
       <c r="A44" s="68">
         <v>36</v>
       </c>
-      <c r="B44" s="67" t="s">
+      <c r="B44" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="67" t="s">
+      <c r="C44" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="67" t="s">
+      <c r="D44" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="67" t="s">
+      <c r="E44" s="66" t="s">
         <v>37</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G44" s="69">
+      <c r="G44" s="70">
         <v>46099</v>
       </c>
-      <c r="H44" s="70" t="s">
+      <c r="H44" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="I44" s="66" t="s">
+      <c r="I44" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J44" s="66" t="s">
+      <c r="J44" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="K44" s="66"/>
+      <c r="K44" s="69"/>
       <c r="L44" s="65"/>
-      <c r="M44" s="67" t="s">
+      <c r="M44" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="N44" s="66"/>
+      <c r="N44" s="69"/>
       <c r="O44" s="65" t="s">
         <v>121</v>
       </c>
@@ -4427,21 +4430,21 @@
     </row>
     <row r="45" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A45" s="68"/>
-      <c r="B45" s="67"/>
-      <c r="C45" s="67"/>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
+      <c r="B45" s="66"/>
+      <c r="C45" s="66"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
       <c r="F45" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G45" s="69"/>
-      <c r="H45" s="70"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="66"/>
-      <c r="K45" s="66"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="69"/>
       <c r="L45" s="65"/>
-      <c r="M45" s="67"/>
-      <c r="N45" s="66"/>
+      <c r="M45" s="66"/>
+      <c r="N45" s="69"/>
       <c r="O45" s="65"/>
       <c r="P45" s="65"/>
       <c r="Q45" s="65"/>
@@ -4498,36 +4501,36 @@
       <c r="B47" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="C47" s="67" t="s">
+      <c r="C47" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="D47" s="67" t="s">
+      <c r="D47" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="67" t="s">
+      <c r="E47" s="66" t="s">
         <v>142</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="G47" s="69">
+      <c r="G47" s="70">
         <v>46099</v>
       </c>
-      <c r="H47" s="70" t="s">
+      <c r="H47" s="73" t="s">
         <v>144</v>
       </c>
       <c r="I47" s="65"/>
-      <c r="J47" s="66" t="s">
+      <c r="J47" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K47" s="66" t="s">
+      <c r="K47" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L47" s="65"/>
-      <c r="M47" s="67" t="s">
+      <c r="M47" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="N47" s="66"/>
+      <c r="N47" s="69"/>
       <c r="O47" s="65" t="s">
         <v>53</v>
       </c>
@@ -4541,20 +4544,20 @@
       <c r="B48" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C48" s="67"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
       <c r="F48" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="G48" s="69"/>
-      <c r="H48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="73"/>
       <c r="I48" s="65"/>
-      <c r="J48" s="66"/>
-      <c r="K48" s="66"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
       <c r="L48" s="65"/>
-      <c r="M48" s="67"/>
-      <c r="N48" s="66"/>
+      <c r="M48" s="66"/>
+      <c r="N48" s="69"/>
       <c r="O48" s="65"/>
       <c r="P48" s="65"/>
       <c r="Q48" s="65"/>
@@ -4656,36 +4659,36 @@
       <c r="B51" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="C51" s="67" t="s">
+      <c r="C51" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="67" t="s">
+      <c r="D51" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="84" t="s">
+      <c r="F51" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="G51" s="69">
+      <c r="G51" s="70">
         <v>46099</v>
       </c>
-      <c r="H51" s="70" t="s">
+      <c r="H51" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="I51" s="66" t="s">
+      <c r="I51" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J51" s="66" t="s">
+      <c r="J51" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="K51" s="66"/>
+      <c r="K51" s="69"/>
       <c r="L51" s="65"/>
       <c r="M51" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="N51" s="66"/>
+      <c r="N51" s="69"/>
       <c r="O51" s="65" t="s">
         <v>102</v>
       </c>
@@ -4699,18 +4702,18 @@
       <c r="B52" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="67"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="84"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="66"/>
-      <c r="J52" s="66"/>
-      <c r="K52" s="66"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="72"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="69"/>
       <c r="L52" s="65"/>
       <c r="M52" s="41"/>
-      <c r="N52" s="66"/>
+      <c r="N52" s="69"/>
       <c r="O52" s="65"/>
       <c r="P52" s="65"/>
       <c r="Q52" s="65"/>
@@ -4718,20 +4721,20 @@
     <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53" s="68"/>
       <c r="B53" s="16"/>
-      <c r="C53" s="67"/>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="84"/>
-      <c r="G53" s="69"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="66"/>
-      <c r="J53" s="66"/>
-      <c r="K53" s="66"/>
+      <c r="C53" s="66"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="72"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="69"/>
       <c r="L53" s="65"/>
       <c r="M53" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="N53" s="66"/>
+      <c r="N53" s="69"/>
       <c r="O53" s="65"/>
       <c r="P53" s="65"/>
       <c r="Q53" s="65"/>
@@ -4755,25 +4758,25 @@
       <c r="F54" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="G54" s="77">
+      <c r="G54" s="75">
         <v>46100</v>
       </c>
-      <c r="H54" s="73" t="s">
+      <c r="H54" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="I54" s="73" t="s">
+      <c r="I54" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="J54" s="71"/>
-      <c r="K54" s="71"/>
+      <c r="J54" s="67"/>
+      <c r="K54" s="67"/>
       <c r="L54" s="65"/>
-      <c r="M54" s="67"/>
-      <c r="N54" s="66"/>
-      <c r="O54" s="72" t="s">
+      <c r="M54" s="66"/>
+      <c r="N54" s="69"/>
+      <c r="O54" s="77" t="s">
         <v>59</v>
       </c>
       <c r="P54" s="65"/>
-      <c r="Q54" s="72" t="s">
+      <c r="Q54" s="77" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4786,55 +4789,55 @@
       <c r="F55" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="G55" s="77"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="73"/>
-      <c r="J55" s="71"/>
-      <c r="K55" s="71"/>
+      <c r="G55" s="75"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76"/>
+      <c r="J55" s="67"/>
+      <c r="K55" s="67"/>
       <c r="L55" s="65"/>
-      <c r="M55" s="67"/>
-      <c r="N55" s="66"/>
-      <c r="O55" s="72"/>
+      <c r="M55" s="66"/>
+      <c r="N55" s="69"/>
+      <c r="O55" s="77"/>
       <c r="P55" s="65"/>
-      <c r="Q55" s="72"/>
+      <c r="Q55" s="77"/>
     </row>
     <row r="56" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A56" s="68">
         <v>43</v>
       </c>
-      <c r="B56" s="67" t="s">
+      <c r="B56" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="C56" s="67" t="s">
+      <c r="C56" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="67" t="s">
+      <c r="D56" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="67" t="s">
+      <c r="E56" s="66" t="s">
         <v>20</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="G56" s="69">
+      <c r="G56" s="70">
         <v>46100</v>
       </c>
-      <c r="H56" s="70" t="s">
+      <c r="H56" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="I56" s="66" t="s">
+      <c r="I56" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J56" s="66" t="s">
+      <c r="J56" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="66" t="s">
+      <c r="K56" s="69" t="s">
         <v>83</v>
       </c>
       <c r="L56" s="65"/>
-      <c r="M56" s="67"/>
-      <c r="N56" s="66"/>
+      <c r="M56" s="66"/>
+      <c r="N56" s="69"/>
       <c r="O56" s="65" t="s">
         <v>108</v>
       </c>
@@ -4845,21 +4848,21 @@
     </row>
     <row r="57" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A57" s="68"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="66"/>
       <c r="F57" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G57" s="69"/>
-      <c r="H57" s="70"/>
-      <c r="I57" s="66"/>
-      <c r="J57" s="66"/>
-      <c r="K57" s="66"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="69"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="69"/>
       <c r="L57" s="65"/>
-      <c r="M57" s="67"/>
-      <c r="N57" s="66"/>
+      <c r="M57" s="66"/>
+      <c r="N57" s="69"/>
       <c r="O57" s="65"/>
       <c r="P57" s="65"/>
       <c r="Q57" s="65"/>
@@ -4868,39 +4871,39 @@
       <c r="A58" s="68">
         <v>44</v>
       </c>
-      <c r="B58" s="67" t="s">
+      <c r="B58" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="C58" s="67" t="s">
+      <c r="C58" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="67" t="s">
+      <c r="D58" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="67" t="s">
+      <c r="E58" s="66" t="s">
         <v>20</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G58" s="69">
+      <c r="G58" s="70">
         <v>46100</v>
       </c>
-      <c r="H58" s="70" t="s">
+      <c r="H58" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="I58" s="66" t="s">
+      <c r="I58" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="J58" s="66" t="s">
+      <c r="J58" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K58" s="66" t="s">
+      <c r="K58" s="69" t="s">
         <v>83</v>
       </c>
       <c r="L58" s="65"/>
-      <c r="M58" s="67"/>
-      <c r="N58" s="66"/>
+      <c r="M58" s="66"/>
+      <c r="N58" s="69"/>
       <c r="O58" s="65" t="s">
         <v>167</v>
       </c>
@@ -4911,40 +4914,40 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59" s="68"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="67"/>
-      <c r="D59" s="67"/>
-      <c r="E59" s="67"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
       <c r="F59" s="11"/>
-      <c r="G59" s="69"/>
-      <c r="H59" s="70"/>
-      <c r="I59" s="66"/>
-      <c r="J59" s="66"/>
-      <c r="K59" s="66"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="69"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="69"/>
       <c r="L59" s="65"/>
-      <c r="M59" s="67"/>
-      <c r="N59" s="66"/>
+      <c r="M59" s="66"/>
+      <c r="N59" s="69"/>
       <c r="O59" s="65"/>
       <c r="P59" s="65"/>
       <c r="Q59" s="65"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60" s="68"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="67"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="66"/>
       <c r="F60" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="G60" s="69"/>
-      <c r="H60" s="70"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="66"/>
-      <c r="K60" s="66"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="73"/>
+      <c r="I60" s="69"/>
+      <c r="J60" s="69"/>
+      <c r="K60" s="69"/>
       <c r="L60" s="65"/>
-      <c r="M60" s="67"/>
-      <c r="N60" s="66"/>
+      <c r="M60" s="66"/>
+      <c r="N60" s="69"/>
       <c r="O60" s="65"/>
       <c r="P60" s="65"/>
       <c r="Q60" s="65"/>
@@ -4968,25 +4971,25 @@
       <c r="F61" s="49" t="s">
         <v>169</v>
       </c>
-      <c r="G61" s="77">
+      <c r="G61" s="75">
         <v>46100</v>
       </c>
-      <c r="H61" s="73" t="s">
+      <c r="H61" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="I61" s="73" t="s">
+      <c r="I61" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="J61" s="71"/>
-      <c r="K61" s="71"/>
+      <c r="J61" s="67"/>
+      <c r="K61" s="67"/>
       <c r="L61" s="65"/>
-      <c r="M61" s="67"/>
-      <c r="N61" s="66"/>
+      <c r="M61" s="66"/>
+      <c r="N61" s="69"/>
       <c r="O61" s="65" t="s">
         <v>59</v>
       </c>
       <c r="P61" s="65"/>
-      <c r="Q61" s="72" t="s">
+      <c r="Q61" s="77" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4999,17 +5002,17 @@
       <c r="F62" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="G62" s="77"/>
-      <c r="H62" s="73"/>
-      <c r="I62" s="73"/>
-      <c r="J62" s="71"/>
-      <c r="K62" s="71"/>
+      <c r="G62" s="75"/>
+      <c r="H62" s="76"/>
+      <c r="I62" s="76"/>
+      <c r="J62" s="67"/>
+      <c r="K62" s="67"/>
       <c r="L62" s="65"/>
-      <c r="M62" s="67"/>
-      <c r="N62" s="66"/>
+      <c r="M62" s="66"/>
+      <c r="N62" s="69"/>
       <c r="O62" s="65"/>
       <c r="P62" s="65"/>
-      <c r="Q62" s="72"/>
+      <c r="Q62" s="77"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63" s="74"/>
@@ -5018,17 +5021,17 @@
       <c r="D63" s="74"/>
       <c r="E63" s="74"/>
       <c r="F63" s="19"/>
-      <c r="G63" s="77"/>
-      <c r="H63" s="73"/>
-      <c r="I63" s="73"/>
-      <c r="J63" s="71"/>
-      <c r="K63" s="71"/>
+      <c r="G63" s="75"/>
+      <c r="H63" s="76"/>
+      <c r="I63" s="76"/>
+      <c r="J63" s="67"/>
+      <c r="K63" s="67"/>
       <c r="L63" s="65"/>
-      <c r="M63" s="67"/>
-      <c r="N63" s="66"/>
+      <c r="M63" s="66"/>
+      <c r="N63" s="69"/>
       <c r="O63" s="65"/>
       <c r="P63" s="65"/>
-      <c r="Q63" s="72"/>
+      <c r="Q63" s="77"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64" s="74"/>
@@ -5037,17 +5040,17 @@
       <c r="D64" s="74"/>
       <c r="E64" s="74"/>
       <c r="F64" s="19"/>
-      <c r="G64" s="77"/>
-      <c r="H64" s="73"/>
-      <c r="I64" s="73"/>
-      <c r="J64" s="71"/>
-      <c r="K64" s="71"/>
+      <c r="G64" s="75"/>
+      <c r="H64" s="76"/>
+      <c r="I64" s="76"/>
+      <c r="J64" s="67"/>
+      <c r="K64" s="67"/>
       <c r="L64" s="65"/>
-      <c r="M64" s="67"/>
-      <c r="N64" s="66"/>
+      <c r="M64" s="66"/>
+      <c r="N64" s="69"/>
       <c r="O64" s="65"/>
       <c r="P64" s="65"/>
-      <c r="Q64" s="72"/>
+      <c r="Q64" s="77"/>
     </row>
     <row r="65" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A65" s="74"/>
@@ -5058,17 +5061,17 @@
       <c r="F65" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="G65" s="77"/>
-      <c r="H65" s="73"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="71"/>
-      <c r="K65" s="71"/>
+      <c r="G65" s="75"/>
+      <c r="H65" s="76"/>
+      <c r="I65" s="76"/>
+      <c r="J65" s="67"/>
+      <c r="K65" s="67"/>
       <c r="L65" s="65"/>
-      <c r="M65" s="67"/>
-      <c r="N65" s="66"/>
+      <c r="M65" s="66"/>
+      <c r="N65" s="69"/>
       <c r="O65" s="65"/>
       <c r="P65" s="65"/>
-      <c r="Q65" s="72"/>
+      <c r="Q65" s="77"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A66" s="47">
@@ -5112,93 +5115,93 @@
       </c>
     </row>
     <row r="67" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A67" s="76">
+      <c r="A67" s="78">
         <v>47</v>
       </c>
-      <c r="B67" s="75" t="s">
+      <c r="B67" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="C67" s="75" t="s">
+      <c r="C67" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="75" t="s">
+      <c r="D67" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="75" t="s">
+      <c r="E67" s="79" t="s">
         <v>20</v>
       </c>
       <c r="F67" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="G67" s="77">
+      <c r="G67" s="75">
         <v>46100</v>
       </c>
-      <c r="H67" s="81" t="s">
+      <c r="H67" s="80" t="s">
         <v>42</v>
       </c>
       <c r="I67" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="J67" s="66"/>
-      <c r="K67" s="66"/>
+      <c r="J67" s="69"/>
+      <c r="K67" s="69"/>
       <c r="L67" s="65"/>
-      <c r="M67" s="67"/>
-      <c r="N67" s="66"/>
-      <c r="O67" s="72" t="s">
+      <c r="M67" s="66"/>
+      <c r="N67" s="69"/>
+      <c r="O67" s="77" t="s">
         <v>59</v>
       </c>
       <c r="P67" s="65"/>
-      <c r="Q67" s="72" t="s">
+      <c r="Q67" s="77" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A68" s="76"/>
-      <c r="B68" s="75"/>
-      <c r="C68" s="75"/>
-      <c r="D68" s="75"/>
-      <c r="E68" s="75"/>
+      <c r="A68" s="78"/>
+      <c r="B68" s="79"/>
+      <c r="C68" s="79"/>
+      <c r="D68" s="79"/>
+      <c r="E68" s="79"/>
       <c r="F68" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="G68" s="77"/>
-      <c r="H68" s="81"/>
+      <c r="G68" s="75"/>
+      <c r="H68" s="80"/>
       <c r="I68" s="74"/>
-      <c r="J68" s="66"/>
-      <c r="K68" s="66"/>
+      <c r="J68" s="69"/>
+      <c r="K68" s="69"/>
       <c r="L68" s="65"/>
-      <c r="M68" s="67"/>
-      <c r="N68" s="66"/>
-      <c r="O68" s="72"/>
+      <c r="M68" s="66"/>
+      <c r="N68" s="69"/>
+      <c r="O68" s="77"/>
       <c r="P68" s="65"/>
-      <c r="Q68" s="72"/>
+      <c r="Q68" s="77"/>
     </row>
     <row r="69" spans="1:17" ht="185.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A69" s="76">
+      <c r="A69" s="78">
         <v>48</v>
       </c>
-      <c r="B69" s="75" t="s">
+      <c r="B69" s="79" t="s">
         <v>175</v>
       </c>
-      <c r="C69" s="75" t="s">
+      <c r="C69" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="75" t="s">
+      <c r="D69" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="75" t="s">
+      <c r="E69" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="F69" s="83" t="s">
+      <c r="F69" s="81" t="s">
         <v>176</v>
       </c>
-      <c r="G69" s="77">
+      <c r="G69" s="75">
         <v>46100</v>
       </c>
-      <c r="H69" s="81" t="s">
+      <c r="H69" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="I69" s="72" t="s">
+      <c r="I69" s="77" t="s">
         <v>88</v>
       </c>
       <c r="J69" s="74" t="s">
@@ -5211,35 +5214,35 @@
       <c r="M69" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="N69" s="66"/>
-      <c r="O69" s="72" t="s">
+      <c r="N69" s="69"/>
+      <c r="O69" s="77" t="s">
         <v>59</v>
       </c>
       <c r="P69" s="65"/>
-      <c r="Q69" s="72" t="s">
+      <c r="Q69" s="77" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A70" s="76"/>
-      <c r="B70" s="75"/>
-      <c r="C70" s="75"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="75"/>
-      <c r="F70" s="83"/>
-      <c r="G70" s="77"/>
-      <c r="H70" s="81"/>
-      <c r="I70" s="72"/>
+      <c r="A70" s="78"/>
+      <c r="B70" s="79"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="79"/>
+      <c r="E70" s="79"/>
+      <c r="F70" s="81"/>
+      <c r="G70" s="75"/>
+      <c r="H70" s="80"/>
+      <c r="I70" s="77"/>
       <c r="J70" s="74"/>
       <c r="K70" s="74"/>
       <c r="L70" s="65"/>
       <c r="M70" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="N70" s="66"/>
-      <c r="O70" s="72"/>
+      <c r="N70" s="69"/>
+      <c r="O70" s="77"/>
       <c r="P70" s="65"/>
-      <c r="Q70" s="72"/>
+      <c r="Q70" s="77"/>
     </row>
     <row r="71" spans="1:17" ht="57" x14ac:dyDescent="0.45">
       <c r="A71" s="14">
@@ -5598,167 +5601,167 @@
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A79" s="76">
+      <c r="A79" s="78">
         <v>57</v>
       </c>
-      <c r="B79" s="75" t="s">
+      <c r="B79" s="79" t="s">
         <v>187</v>
       </c>
-      <c r="C79" s="75" t="s">
+      <c r="C79" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="75" t="s">
+      <c r="D79" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E79" s="75" t="s">
+      <c r="E79" s="79" t="s">
         <v>20</v>
       </c>
       <c r="F79" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="G79" s="77">
+      <c r="G79" s="75">
         <v>46100</v>
       </c>
-      <c r="H79" s="81" t="s">
+      <c r="H79" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="I79" s="72" t="s">
+      <c r="I79" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="J79" s="66"/>
-      <c r="K79" s="66"/>
+      <c r="J79" s="69"/>
+      <c r="K79" s="69"/>
       <c r="L79" s="65"/>
-      <c r="M79" s="67"/>
-      <c r="N79" s="66"/>
-      <c r="O79" s="72" t="s">
+      <c r="M79" s="66"/>
+      <c r="N79" s="69"/>
+      <c r="O79" s="77" t="s">
         <v>59</v>
       </c>
       <c r="P79" s="65"/>
-      <c r="Q79" s="72" t="s">
+      <c r="Q79" s="77" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A80" s="76"/>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75"/>
+      <c r="A80" s="78"/>
+      <c r="B80" s="79"/>
+      <c r="C80" s="79"/>
+      <c r="D80" s="79"/>
+      <c r="E80" s="79"/>
       <c r="F80" s="10"/>
-      <c r="G80" s="77"/>
-      <c r="H80" s="81"/>
-      <c r="I80" s="72"/>
-      <c r="J80" s="66"/>
-      <c r="K80" s="66"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="80"/>
+      <c r="I80" s="77"/>
+      <c r="J80" s="69"/>
+      <c r="K80" s="69"/>
       <c r="L80" s="65"/>
-      <c r="M80" s="67"/>
-      <c r="N80" s="66"/>
-      <c r="O80" s="72"/>
+      <c r="M80" s="66"/>
+      <c r="N80" s="69"/>
+      <c r="O80" s="77"/>
       <c r="P80" s="65"/>
-      <c r="Q80" s="72"/>
+      <c r="Q80" s="77"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A81" s="76"/>
-      <c r="B81" s="75"/>
-      <c r="C81" s="75"/>
-      <c r="D81" s="75"/>
-      <c r="E81" s="75"/>
+      <c r="A81" s="78"/>
+      <c r="B81" s="79"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="79"/>
+      <c r="E81" s="79"/>
       <c r="F81" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="G81" s="77"/>
-      <c r="H81" s="81"/>
-      <c r="I81" s="72"/>
-      <c r="J81" s="66"/>
-      <c r="K81" s="66"/>
+      <c r="G81" s="75"/>
+      <c r="H81" s="80"/>
+      <c r="I81" s="77"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69"/>
       <c r="L81" s="65"/>
-      <c r="M81" s="67"/>
-      <c r="N81" s="66"/>
-      <c r="O81" s="72"/>
+      <c r="M81" s="66"/>
+      <c r="N81" s="69"/>
+      <c r="O81" s="77"/>
       <c r="P81" s="65"/>
-      <c r="Q81" s="72"/>
+      <c r="Q81" s="77"/>
     </row>
     <row r="82" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A82" s="76"/>
-      <c r="B82" s="75"/>
-      <c r="C82" s="75"/>
-      <c r="D82" s="75"/>
-      <c r="E82" s="75"/>
+      <c r="A82" s="78"/>
+      <c r="B82" s="79"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="79"/>
       <c r="F82" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="G82" s="77"/>
-      <c r="H82" s="81"/>
-      <c r="I82" s="72"/>
-      <c r="J82" s="66"/>
-      <c r="K82" s="66"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="80"/>
+      <c r="I82" s="77"/>
+      <c r="J82" s="69"/>
+      <c r="K82" s="69"/>
       <c r="L82" s="65"/>
-      <c r="M82" s="67"/>
-      <c r="N82" s="66"/>
-      <c r="O82" s="72"/>
+      <c r="M82" s="66"/>
+      <c r="N82" s="69"/>
+      <c r="O82" s="77"/>
       <c r="P82" s="65"/>
-      <c r="Q82" s="72"/>
+      <c r="Q82" s="77"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A83" s="76"/>
-      <c r="B83" s="75"/>
-      <c r="C83" s="75"/>
-      <c r="D83" s="75"/>
-      <c r="E83" s="75"/>
+      <c r="A83" s="78"/>
+      <c r="B83" s="79"/>
+      <c r="C83" s="79"/>
+      <c r="D83" s="79"/>
+      <c r="E83" s="79"/>
       <c r="F83" s="10"/>
-      <c r="G83" s="77"/>
-      <c r="H83" s="81"/>
-      <c r="I83" s="72"/>
-      <c r="J83" s="66"/>
-      <c r="K83" s="66"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="80"/>
+      <c r="I83" s="77"/>
+      <c r="J83" s="69"/>
+      <c r="K83" s="69"/>
       <c r="L83" s="65"/>
-      <c r="M83" s="67"/>
-      <c r="N83" s="66"/>
-      <c r="O83" s="72"/>
+      <c r="M83" s="66"/>
+      <c r="N83" s="69"/>
+      <c r="O83" s="77"/>
       <c r="P83" s="65"/>
-      <c r="Q83" s="72"/>
+      <c r="Q83" s="77"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A84" s="76"/>
-      <c r="B84" s="75"/>
-      <c r="C84" s="75"/>
-      <c r="D84" s="75"/>
-      <c r="E84" s="75"/>
+      <c r="A84" s="78"/>
+      <c r="B84" s="79"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="79"/>
+      <c r="E84" s="79"/>
       <c r="F84" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="G84" s="77"/>
-      <c r="H84" s="81"/>
-      <c r="I84" s="72"/>
-      <c r="J84" s="66"/>
-      <c r="K84" s="66"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="80"/>
+      <c r="I84" s="77"/>
+      <c r="J84" s="69"/>
+      <c r="K84" s="69"/>
       <c r="L84" s="65"/>
-      <c r="M84" s="67"/>
-      <c r="N84" s="66"/>
-      <c r="O84" s="72"/>
+      <c r="M84" s="66"/>
+      <c r="N84" s="69"/>
+      <c r="O84" s="77"/>
       <c r="P84" s="65"/>
-      <c r="Q84" s="72"/>
+      <c r="Q84" s="77"/>
     </row>
     <row r="85" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A85" s="76"/>
-      <c r="B85" s="75"/>
-      <c r="C85" s="75"/>
-      <c r="D85" s="75"/>
-      <c r="E85" s="75"/>
+      <c r="A85" s="78"/>
+      <c r="B85" s="79"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="79"/>
+      <c r="E85" s="79"/>
       <c r="F85" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="G85" s="77"/>
-      <c r="H85" s="81"/>
-      <c r="I85" s="72"/>
-      <c r="J85" s="66"/>
-      <c r="K85" s="66"/>
+      <c r="G85" s="75"/>
+      <c r="H85" s="80"/>
+      <c r="I85" s="77"/>
+      <c r="J85" s="69"/>
+      <c r="K85" s="69"/>
       <c r="L85" s="65"/>
-      <c r="M85" s="67"/>
-      <c r="N85" s="66"/>
-      <c r="O85" s="72"/>
+      <c r="M85" s="66"/>
+      <c r="N85" s="69"/>
+      <c r="O85" s="77"/>
       <c r="P85" s="65"/>
-      <c r="Q85" s="72"/>
+      <c r="Q85" s="77"/>
     </row>
     <row r="86" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A86" s="14">
@@ -5914,29 +5917,29 @@
       <c r="F89" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="G89" s="77">
+      <c r="G89" s="75">
         <v>46105</v>
       </c>
-      <c r="H89" s="73" t="s">
+      <c r="H89" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="I89" s="73" t="s">
+      <c r="I89" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="J89" s="73" t="s">
+      <c r="J89" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="K89" s="71"/>
+      <c r="K89" s="67"/>
       <c r="L89" s="65"/>
       <c r="M89" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="N89" s="66"/>
-      <c r="O89" s="72" t="s">
+      <c r="N89" s="69"/>
+      <c r="O89" s="77" t="s">
         <v>59</v>
       </c>
       <c r="P89" s="65"/>
-      <c r="Q89" s="72" t="s">
+      <c r="Q89" s="77" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5949,17 +5952,17 @@
       <c r="F90" s="49" t="s">
         <v>212</v>
       </c>
-      <c r="G90" s="77"/>
-      <c r="H90" s="73"/>
-      <c r="I90" s="73"/>
-      <c r="J90" s="73"/>
-      <c r="K90" s="71"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="76"/>
+      <c r="I90" s="76"/>
+      <c r="J90" s="76"/>
+      <c r="K90" s="67"/>
       <c r="L90" s="65"/>
       <c r="M90" s="82"/>
-      <c r="N90" s="66"/>
-      <c r="O90" s="72"/>
+      <c r="N90" s="69"/>
+      <c r="O90" s="77"/>
       <c r="P90" s="65"/>
-      <c r="Q90" s="72"/>
+      <c r="Q90" s="77"/>
     </row>
     <row r="91" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A91" s="12">
@@ -6007,42 +6010,42 @@
       </c>
     </row>
     <row r="92" spans="1:17" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A92" s="66">
+      <c r="A92" s="69">
         <v>63</v>
       </c>
-      <c r="B92" s="66" t="s">
+      <c r="B92" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="C92" s="66" t="s">
+      <c r="C92" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D92" s="66" t="s">
+      <c r="D92" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E92" s="66" t="s">
+      <c r="E92" s="69" t="s">
         <v>20</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="G92" s="69">
+      <c r="G92" s="70">
         <v>46105</v>
       </c>
-      <c r="H92" s="71" t="s">
+      <c r="H92" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="I92" s="71" t="s">
+      <c r="I92" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J92" s="71" t="s">
+      <c r="J92" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="K92" s="66"/>
+      <c r="K92" s="69"/>
       <c r="L92" s="65"/>
-      <c r="M92" s="67" t="s">
+      <c r="M92" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="N92" s="66"/>
+      <c r="N92" s="69"/>
       <c r="O92" s="65" t="s">
         <v>102</v>
       </c>
@@ -6052,22 +6055,22 @@
       </c>
     </row>
     <row r="93" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A93" s="66"/>
-      <c r="B93" s="66"/>
-      <c r="C93" s="66"/>
-      <c r="D93" s="66"/>
-      <c r="E93" s="66"/>
+      <c r="A93" s="69"/>
+      <c r="B93" s="69"/>
+      <c r="C93" s="69"/>
+      <c r="D93" s="69"/>
+      <c r="E93" s="69"/>
       <c r="F93" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="G93" s="69"/>
-      <c r="H93" s="71"/>
-      <c r="I93" s="71"/>
-      <c r="J93" s="71"/>
-      <c r="K93" s="66"/>
+      <c r="G93" s="70"/>
+      <c r="H93" s="67"/>
+      <c r="I93" s="67"/>
+      <c r="J93" s="67"/>
+      <c r="K93" s="69"/>
       <c r="L93" s="65"/>
-      <c r="M93" s="67"/>
-      <c r="N93" s="66"/>
+      <c r="M93" s="66"/>
+      <c r="N93" s="69"/>
       <c r="O93" s="65"/>
       <c r="P93" s="65"/>
       <c r="Q93" s="65"/>
@@ -6119,41 +6122,41 @@
       <c r="A95" s="68">
         <v>65</v>
       </c>
-      <c r="B95" s="67" t="s">
+      <c r="B95" s="66" t="s">
         <v>221</v>
       </c>
-      <c r="C95" s="66" t="s">
+      <c r="C95" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D95" s="66" t="s">
+      <c r="D95" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E95" s="66" t="s">
+      <c r="E95" s="69" t="s">
         <v>20</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G95" s="69">
+      <c r="G95" s="70">
         <v>46108</v>
       </c>
-      <c r="H95" s="70" t="s">
+      <c r="H95" s="73" t="s">
         <v>207</v>
       </c>
       <c r="I95" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="J95" s="66" t="s">
+      <c r="J95" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K95" s="66" t="s">
+      <c r="K95" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L95" s="65"/>
-      <c r="M95" s="67" t="s">
+      <c r="M95" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="N95" s="66"/>
+      <c r="N95" s="69"/>
       <c r="O95" s="65" t="s">
         <v>111</v>
       </c>
@@ -6164,84 +6167,84 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A96" s="68"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="66"/>
-      <c r="D96" s="66"/>
-      <c r="E96" s="66"/>
+      <c r="B96" s="66"/>
+      <c r="C96" s="69"/>
+      <c r="D96" s="69"/>
+      <c r="E96" s="69"/>
       <c r="F96" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="G96" s="69"/>
-      <c r="H96" s="70"/>
+      <c r="G96" s="70"/>
+      <c r="H96" s="73"/>
       <c r="I96" s="65"/>
-      <c r="J96" s="66"/>
-      <c r="K96" s="66"/>
+      <c r="J96" s="69"/>
+      <c r="K96" s="69"/>
       <c r="L96" s="65"/>
-      <c r="M96" s="67"/>
-      <c r="N96" s="66"/>
+      <c r="M96" s="66"/>
+      <c r="N96" s="69"/>
       <c r="O96" s="65"/>
       <c r="P96" s="65"/>
       <c r="Q96" s="65"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A97" s="68"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="66"/>
-      <c r="D97" s="66"/>
-      <c r="E97" s="66"/>
+      <c r="B97" s="66"/>
+      <c r="C97" s="69"/>
+      <c r="D97" s="69"/>
+      <c r="E97" s="69"/>
       <c r="F97" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="G97" s="69"/>
-      <c r="H97" s="70"/>
+      <c r="G97" s="70"/>
+      <c r="H97" s="73"/>
       <c r="I97" s="65"/>
-      <c r="J97" s="66"/>
-      <c r="K97" s="66"/>
+      <c r="J97" s="69"/>
+      <c r="K97" s="69"/>
       <c r="L97" s="65"/>
-      <c r="M97" s="67"/>
-      <c r="N97" s="66"/>
+      <c r="M97" s="66"/>
+      <c r="N97" s="69"/>
       <c r="O97" s="65"/>
       <c r="P97" s="65"/>
       <c r="Q97" s="65"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A98" s="68"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="66"/>
-      <c r="D98" s="66"/>
-      <c r="E98" s="66"/>
+      <c r="B98" s="66"/>
+      <c r="C98" s="69"/>
+      <c r="D98" s="69"/>
+      <c r="E98" s="69"/>
       <c r="F98" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="G98" s="69"/>
-      <c r="H98" s="70"/>
+      <c r="G98" s="70"/>
+      <c r="H98" s="73"/>
       <c r="I98" s="65"/>
-      <c r="J98" s="66"/>
-      <c r="K98" s="66"/>
+      <c r="J98" s="69"/>
+      <c r="K98" s="69"/>
       <c r="L98" s="65"/>
-      <c r="M98" s="67"/>
-      <c r="N98" s="66"/>
+      <c r="M98" s="66"/>
+      <c r="N98" s="69"/>
       <c r="O98" s="65"/>
       <c r="P98" s="65"/>
       <c r="Q98" s="65"/>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A99" s="68"/>
-      <c r="B99" s="67"/>
-      <c r="C99" s="66"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="66"/>
+      <c r="B99" s="66"/>
+      <c r="C99" s="69"/>
+      <c r="D99" s="69"/>
+      <c r="E99" s="69"/>
       <c r="F99" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="G99" s="69"/>
-      <c r="H99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="73"/>
       <c r="I99" s="65"/>
-      <c r="J99" s="66"/>
-      <c r="K99" s="66"/>
+      <c r="J99" s="69"/>
+      <c r="K99" s="69"/>
       <c r="L99" s="65"/>
-      <c r="M99" s="67"/>
-      <c r="N99" s="66"/>
+      <c r="M99" s="66"/>
+      <c r="N99" s="69"/>
       <c r="O99" s="65"/>
       <c r="P99" s="65"/>
       <c r="Q99" s="65"/>
@@ -6426,67 +6429,67 @@
       <c r="A104" s="68">
         <v>70</v>
       </c>
-      <c r="B104" s="67" t="s">
+      <c r="B104" s="66" t="s">
         <v>233</v>
       </c>
-      <c r="C104" s="67" t="s">
+      <c r="C104" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D104" s="67" t="s">
+      <c r="D104" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E104" s="67" t="s">
+      <c r="E104" s="66" t="s">
         <v>20</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="G104" s="69">
+      <c r="G104" s="70">
         <v>46057</v>
       </c>
-      <c r="H104" s="80" t="s">
+      <c r="H104" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="I104" s="79" t="s">
+      <c r="I104" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="J104" s="71" t="s">
+      <c r="J104" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="K104" s="71" t="s">
+      <c r="K104" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="L104" s="79"/>
-      <c r="M104" s="79" t="s">
+      <c r="L104" s="84"/>
+      <c r="M104" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="N104" s="71"/>
-      <c r="O104" s="79" t="s">
+      <c r="N104" s="67"/>
+      <c r="O104" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="P104" s="79"/>
-      <c r="Q104" s="79"/>
+      <c r="P104" s="84"/>
+      <c r="Q104" s="84"/>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A105" s="68"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="67"/>
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
+      <c r="B105" s="66"/>
+      <c r="C105" s="66"/>
+      <c r="D105" s="66"/>
+      <c r="E105" s="66"/>
       <c r="F105" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="G105" s="69"/>
-      <c r="H105" s="80"/>
-      <c r="I105" s="79"/>
-      <c r="J105" s="71"/>
-      <c r="K105" s="71"/>
-      <c r="L105" s="79"/>
-      <c r="M105" s="79"/>
-      <c r="N105" s="71"/>
-      <c r="O105" s="79"/>
-      <c r="P105" s="79"/>
-      <c r="Q105" s="79"/>
+      <c r="G105" s="70"/>
+      <c r="H105" s="83"/>
+      <c r="I105" s="84"/>
+      <c r="J105" s="67"/>
+      <c r="K105" s="67"/>
+      <c r="L105" s="84"/>
+      <c r="M105" s="84"/>
+      <c r="N105" s="67"/>
+      <c r="O105" s="84"/>
+      <c r="P105" s="84"/>
+      <c r="Q105" s="84"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A106" s="14">
@@ -6747,41 +6750,41 @@
       <c r="Q111" s="39"/>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A112" s="76">
+      <c r="A112" s="78">
         <v>77</v>
       </c>
-      <c r="B112" s="75" t="s">
+      <c r="B112" s="79" t="s">
         <v>242</v>
       </c>
-      <c r="C112" s="75" t="s">
+      <c r="C112" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="D112" s="75" t="s">
+      <c r="D112" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E112" s="75" t="s">
+      <c r="E112" s="79" t="s">
         <v>20</v>
       </c>
       <c r="F112" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="G112" s="77">
+      <c r="G112" s="75">
         <v>46114</v>
       </c>
-      <c r="H112" s="81" t="s">
+      <c r="H112" s="80" t="s">
         <v>238</v>
       </c>
       <c r="I112" s="65"/>
-      <c r="J112" s="66" t="s">
+      <c r="J112" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K112" s="66" t="s">
+      <c r="K112" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L112" s="65"/>
-      <c r="M112" s="67"/>
-      <c r="N112" s="66"/>
-      <c r="O112" s="72" t="s">
+      <c r="M112" s="66"/>
+      <c r="N112" s="69"/>
+      <c r="O112" s="77" t="s">
         <v>59</v>
       </c>
       <c r="P112" s="65"/>
@@ -6790,23 +6793,23 @@
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A113" s="76"/>
-      <c r="B113" s="75"/>
-      <c r="C113" s="75"/>
-      <c r="D113" s="75"/>
-      <c r="E113" s="75"/>
+      <c r="A113" s="78"/>
+      <c r="B113" s="79"/>
+      <c r="C113" s="79"/>
+      <c r="D113" s="79"/>
+      <c r="E113" s="79"/>
       <c r="F113" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="G113" s="77"/>
-      <c r="H113" s="81"/>
+      <c r="G113" s="75"/>
+      <c r="H113" s="80"/>
       <c r="I113" s="65"/>
-      <c r="J113" s="66"/>
-      <c r="K113" s="66"/>
+      <c r="J113" s="69"/>
+      <c r="K113" s="69"/>
       <c r="L113" s="65"/>
-      <c r="M113" s="67"/>
-      <c r="N113" s="66"/>
-      <c r="O113" s="72"/>
+      <c r="M113" s="66"/>
+      <c r="N113" s="69"/>
+      <c r="O113" s="77"/>
       <c r="P113" s="65"/>
       <c r="Q113" s="65"/>
     </row>
@@ -6982,69 +6985,69 @@
       <c r="A118" s="68">
         <v>82</v>
       </c>
-      <c r="B118" s="67" t="s">
+      <c r="B118" s="66" t="s">
         <v>265</v>
       </c>
-      <c r="C118" s="67" t="s">
+      <c r="C118" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D118" s="67" t="s">
+      <c r="D118" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E118" s="67" t="s">
+      <c r="E118" s="66" t="s">
         <v>20</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="G118" s="69">
+      <c r="G118" s="70">
         <v>46085</v>
       </c>
-      <c r="H118" s="80" t="s">
+      <c r="H118" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="I118" s="79" t="s">
+      <c r="I118" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="J118" s="71" t="s">
+      <c r="J118" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="K118" s="71" t="s">
+      <c r="K118" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="L118" s="79"/>
-      <c r="M118" s="79" t="s">
+      <c r="L118" s="84"/>
+      <c r="M118" s="84" t="s">
         <v>268</v>
       </c>
-      <c r="N118" s="71"/>
+      <c r="N118" s="67"/>
       <c r="O118" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="P118" s="79"/>
-      <c r="Q118" s="79" t="s">
+      <c r="P118" s="84"/>
+      <c r="Q118" s="84" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A119" s="68"/>
-      <c r="B119" s="67"/>
-      <c r="C119" s="67"/>
-      <c r="D119" s="67"/>
-      <c r="E119" s="67"/>
+      <c r="B119" s="66"/>
+      <c r="C119" s="66"/>
+      <c r="D119" s="66"/>
+      <c r="E119" s="66"/>
       <c r="F119" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="G119" s="69"/>
-      <c r="H119" s="80"/>
-      <c r="I119" s="79"/>
-      <c r="J119" s="71"/>
-      <c r="K119" s="71"/>
-      <c r="L119" s="79"/>
-      <c r="M119" s="79"/>
-      <c r="N119" s="71"/>
+      <c r="G119" s="70"/>
+      <c r="H119" s="83"/>
+      <c r="I119" s="84"/>
+      <c r="J119" s="67"/>
+      <c r="K119" s="67"/>
+      <c r="L119" s="84"/>
+      <c r="M119" s="84"/>
+      <c r="N119" s="67"/>
       <c r="O119" s="65"/>
-      <c r="P119" s="79"/>
-      <c r="Q119" s="79"/>
+      <c r="P119" s="84"/>
+      <c r="Q119" s="84"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A120" s="14">
@@ -7183,37 +7186,37 @@
       <c r="A123" s="68">
         <v>86</v>
       </c>
-      <c r="B123" s="67" t="s">
+      <c r="B123" s="66" t="s">
         <v>272</v>
       </c>
-      <c r="C123" s="67" t="s">
+      <c r="C123" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D123" s="66" t="s">
+      <c r="D123" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E123" s="67"/>
+      <c r="E123" s="66"/>
       <c r="F123" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="G123" s="69">
+      <c r="G123" s="70">
         <v>46118</v>
       </c>
-      <c r="H123" s="70" t="s">
+      <c r="H123" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="I123" s="79" t="s">
+      <c r="I123" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="J123" s="66" t="s">
+      <c r="J123" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="K123" s="66"/>
+      <c r="K123" s="69"/>
       <c r="L123" s="65"/>
       <c r="M123" s="44" t="s">
         <v>279</v>
       </c>
-      <c r="N123" s="66"/>
+      <c r="N123" s="69"/>
       <c r="O123" s="65" t="s">
         <v>59</v>
       </c>
@@ -7224,23 +7227,23 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A124" s="68"/>
-      <c r="B124" s="67"/>
-      <c r="C124" s="67"/>
-      <c r="D124" s="66"/>
-      <c r="E124" s="67"/>
+      <c r="B124" s="66"/>
+      <c r="C124" s="66"/>
+      <c r="D124" s="69"/>
+      <c r="E124" s="66"/>
       <c r="F124" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="G124" s="69"/>
-      <c r="H124" s="70"/>
-      <c r="I124" s="79"/>
-      <c r="J124" s="66"/>
-      <c r="K124" s="66"/>
+      <c r="G124" s="70"/>
+      <c r="H124" s="73"/>
+      <c r="I124" s="84"/>
+      <c r="J124" s="69"/>
+      <c r="K124" s="69"/>
       <c r="L124" s="65"/>
       <c r="M124" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="N124" s="66"/>
+      <c r="N124" s="69"/>
       <c r="O124" s="65"/>
       <c r="P124" s="65"/>
       <c r="Q124" s="65"/>
@@ -7249,39 +7252,39 @@
       <c r="A125" s="68">
         <v>87</v>
       </c>
-      <c r="B125" s="67" t="s">
+      <c r="B125" s="66" t="s">
         <v>272</v>
       </c>
-      <c r="C125" s="67" t="s">
+      <c r="C125" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D125" s="66" t="s">
+      <c r="D125" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E125" s="67"/>
+      <c r="E125" s="66"/>
       <c r="F125" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="G125" s="69">
+      <c r="G125" s="70">
         <v>46118</v>
       </c>
-      <c r="H125" s="70" t="s">
+      <c r="H125" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="I125" s="79" t="s">
+      <c r="I125" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="J125" s="66" t="s">
+      <c r="J125" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K125" s="66" t="s">
+      <c r="K125" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L125" s="65"/>
       <c r="M125" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="N125" s="66"/>
+      <c r="N125" s="69"/>
       <c r="O125" s="65" t="s">
         <v>59</v>
       </c>
@@ -7292,23 +7295,23 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A126" s="68"/>
-      <c r="B126" s="67"/>
-      <c r="C126" s="67"/>
-      <c r="D126" s="66"/>
-      <c r="E126" s="67"/>
+      <c r="B126" s="66"/>
+      <c r="C126" s="66"/>
+      <c r="D126" s="69"/>
+      <c r="E126" s="66"/>
       <c r="F126" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="G126" s="69"/>
-      <c r="H126" s="70"/>
-      <c r="I126" s="79"/>
-      <c r="J126" s="66"/>
-      <c r="K126" s="66"/>
+      <c r="G126" s="70"/>
+      <c r="H126" s="73"/>
+      <c r="I126" s="84"/>
+      <c r="J126" s="69"/>
+      <c r="K126" s="69"/>
       <c r="L126" s="65"/>
       <c r="M126" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="N126" s="66"/>
+      <c r="N126" s="69"/>
       <c r="O126" s="65"/>
       <c r="P126" s="65"/>
       <c r="Q126" s="65"/>
@@ -7317,37 +7320,37 @@
       <c r="A127" s="68">
         <v>88</v>
       </c>
-      <c r="B127" s="67" t="s">
+      <c r="B127" s="66" t="s">
         <v>272</v>
       </c>
-      <c r="C127" s="67" t="s">
+      <c r="C127" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D127" s="66" t="s">
+      <c r="D127" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E127" s="67"/>
+      <c r="E127" s="66"/>
       <c r="F127" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="G127" s="69">
+      <c r="G127" s="70">
         <v>46118</v>
       </c>
-      <c r="H127" s="70" t="s">
+      <c r="H127" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="I127" s="79" t="s">
+      <c r="I127" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="J127" s="66" t="s">
+      <c r="J127" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="K127" s="66"/>
+      <c r="K127" s="69"/>
       <c r="L127" s="65"/>
-      <c r="M127" s="67" t="s">
+      <c r="M127" s="66" t="s">
         <v>286</v>
       </c>
-      <c r="N127" s="66"/>
+      <c r="N127" s="69"/>
       <c r="O127" s="65" t="s">
         <v>59</v>
       </c>
@@ -7358,42 +7361,42 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A128" s="68"/>
-      <c r="B128" s="67"/>
-      <c r="C128" s="67"/>
-      <c r="D128" s="66"/>
-      <c r="E128" s="67"/>
+      <c r="B128" s="66"/>
+      <c r="C128" s="66"/>
+      <c r="D128" s="69"/>
+      <c r="E128" s="66"/>
       <c r="F128" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="G128" s="69"/>
-      <c r="H128" s="70"/>
-      <c r="I128" s="79"/>
-      <c r="J128" s="66"/>
-      <c r="K128" s="66"/>
+      <c r="G128" s="70"/>
+      <c r="H128" s="73"/>
+      <c r="I128" s="84"/>
+      <c r="J128" s="69"/>
+      <c r="K128" s="69"/>
       <c r="L128" s="65"/>
-      <c r="M128" s="67"/>
-      <c r="N128" s="66"/>
+      <c r="M128" s="66"/>
+      <c r="N128" s="69"/>
       <c r="O128" s="65"/>
       <c r="P128" s="65"/>
       <c r="Q128" s="65"/>
     </row>
     <row r="129" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A129" s="68"/>
-      <c r="B129" s="67"/>
-      <c r="C129" s="67"/>
-      <c r="D129" s="66"/>
-      <c r="E129" s="67"/>
+      <c r="B129" s="66"/>
+      <c r="C129" s="66"/>
+      <c r="D129" s="69"/>
+      <c r="E129" s="66"/>
       <c r="F129" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="G129" s="69"/>
-      <c r="H129" s="70"/>
-      <c r="I129" s="79"/>
-      <c r="J129" s="66"/>
-      <c r="K129" s="66"/>
+      <c r="G129" s="70"/>
+      <c r="H129" s="73"/>
+      <c r="I129" s="84"/>
+      <c r="J129" s="69"/>
+      <c r="K129" s="69"/>
       <c r="L129" s="65"/>
-      <c r="M129" s="67"/>
-      <c r="N129" s="66"/>
+      <c r="M129" s="66"/>
+      <c r="N129" s="69"/>
       <c r="O129" s="65"/>
       <c r="P129" s="65"/>
       <c r="Q129" s="65"/>
@@ -7402,37 +7405,37 @@
       <c r="A130" s="68">
         <v>89</v>
       </c>
-      <c r="B130" s="67" t="s">
+      <c r="B130" s="66" t="s">
         <v>287</v>
       </c>
-      <c r="C130" s="67" t="s">
+      <c r="C130" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D130" s="66" t="s">
+      <c r="D130" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E130" s="67"/>
+      <c r="E130" s="66"/>
       <c r="F130" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="G130" s="69">
+      <c r="G130" s="70">
         <v>46118</v>
       </c>
-      <c r="H130" s="70" t="s">
+      <c r="H130" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="I130" s="79" t="s">
+      <c r="I130" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="J130" s="66" t="s">
+      <c r="J130" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="K130" s="66"/>
+      <c r="K130" s="69"/>
       <c r="L130" s="65"/>
-      <c r="M130" s="78" t="s">
+      <c r="M130" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="N130" s="66"/>
+      <c r="N130" s="69"/>
       <c r="O130" s="65" t="s">
         <v>48</v>
       </c>
@@ -7443,21 +7446,21 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A131" s="68"/>
-      <c r="B131" s="67"/>
-      <c r="C131" s="67"/>
-      <c r="D131" s="66"/>
-      <c r="E131" s="67"/>
+      <c r="B131" s="66"/>
+      <c r="C131" s="66"/>
+      <c r="D131" s="69"/>
+      <c r="E131" s="66"/>
       <c r="F131" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="G131" s="69"/>
-      <c r="H131" s="70"/>
-      <c r="I131" s="79"/>
-      <c r="J131" s="66"/>
-      <c r="K131" s="66"/>
+      <c r="G131" s="70"/>
+      <c r="H131" s="73"/>
+      <c r="I131" s="84"/>
+      <c r="J131" s="69"/>
+      <c r="K131" s="69"/>
       <c r="L131" s="65"/>
-      <c r="M131" s="78"/>
-      <c r="N131" s="66"/>
+      <c r="M131" s="85"/>
+      <c r="N131" s="69"/>
       <c r="O131" s="65"/>
       <c r="P131" s="65"/>
       <c r="Q131" s="65"/>
@@ -7466,37 +7469,37 @@
       <c r="A132" s="68">
         <v>90</v>
       </c>
-      <c r="B132" s="66" t="s">
+      <c r="B132" s="69" t="s">
         <v>287</v>
       </c>
-      <c r="C132" s="66" t="s">
+      <c r="C132" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D132" s="66" t="s">
+      <c r="D132" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E132" s="66"/>
+      <c r="E132" s="69"/>
       <c r="F132" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="G132" s="69">
+      <c r="G132" s="70">
         <v>46118</v>
       </c>
-      <c r="H132" s="71" t="s">
+      <c r="H132" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="I132" s="71" t="s">
+      <c r="I132" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J132" s="66" t="s">
+      <c r="J132" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="K132" s="66"/>
+      <c r="K132" s="69"/>
       <c r="L132" s="65"/>
-      <c r="M132" s="67" t="s">
+      <c r="M132" s="66" t="s">
         <v>293</v>
       </c>
-      <c r="N132" s="66"/>
+      <c r="N132" s="69"/>
       <c r="O132" s="65" t="s">
         <v>59</v>
       </c>
@@ -7507,21 +7510,21 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A133" s="68"/>
-      <c r="B133" s="66"/>
-      <c r="C133" s="66"/>
-      <c r="D133" s="66"/>
-      <c r="E133" s="66"/>
+      <c r="B133" s="69"/>
+      <c r="C133" s="69"/>
+      <c r="D133" s="69"/>
+      <c r="E133" s="69"/>
       <c r="F133" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="G133" s="69"/>
-      <c r="H133" s="71"/>
-      <c r="I133" s="71"/>
-      <c r="J133" s="66"/>
-      <c r="K133" s="66"/>
+      <c r="G133" s="70"/>
+      <c r="H133" s="67"/>
+      <c r="I133" s="67"/>
+      <c r="J133" s="69"/>
+      <c r="K133" s="69"/>
       <c r="L133" s="65"/>
-      <c r="M133" s="67"/>
-      <c r="N133" s="66"/>
+      <c r="M133" s="66"/>
+      <c r="N133" s="69"/>
       <c r="O133" s="65"/>
       <c r="P133" s="65"/>
       <c r="Q133" s="65"/>
@@ -7530,37 +7533,37 @@
       <c r="A134" s="68">
         <v>91</v>
       </c>
-      <c r="B134" s="66" t="s">
+      <c r="B134" s="69" t="s">
         <v>272</v>
       </c>
-      <c r="C134" s="66" t="s">
+      <c r="C134" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D134" s="66" t="s">
+      <c r="D134" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E134" s="66"/>
+      <c r="E134" s="69"/>
       <c r="F134" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="G134" s="69">
+      <c r="G134" s="70">
         <v>46118</v>
       </c>
-      <c r="H134" s="71" t="s">
+      <c r="H134" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="I134" s="71" t="s">
+      <c r="I134" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J134" s="66" t="s">
+      <c r="J134" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="K134" s="66"/>
+      <c r="K134" s="69"/>
       <c r="L134" s="65"/>
-      <c r="M134" s="78" t="s">
+      <c r="M134" s="85" t="s">
         <v>295</v>
       </c>
-      <c r="N134" s="66"/>
+      <c r="N134" s="69"/>
       <c r="O134" s="65" t="s">
         <v>59</v>
       </c>
@@ -7571,21 +7574,21 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A135" s="68"/>
-      <c r="B135" s="66"/>
-      <c r="C135" s="66"/>
-      <c r="D135" s="66"/>
-      <c r="E135" s="66"/>
+      <c r="B135" s="69"/>
+      <c r="C135" s="69"/>
+      <c r="D135" s="69"/>
+      <c r="E135" s="69"/>
       <c r="F135" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="G135" s="69"/>
-      <c r="H135" s="71"/>
-      <c r="I135" s="71"/>
-      <c r="J135" s="66"/>
-      <c r="K135" s="66"/>
+      <c r="G135" s="70"/>
+      <c r="H135" s="67"/>
+      <c r="I135" s="67"/>
+      <c r="J135" s="69"/>
+      <c r="K135" s="69"/>
       <c r="L135" s="65"/>
-      <c r="M135" s="78"/>
-      <c r="N135" s="66"/>
+      <c r="M135" s="85"/>
+      <c r="N135" s="69"/>
       <c r="O135" s="65"/>
       <c r="P135" s="65"/>
       <c r="Q135" s="65"/>
@@ -7594,39 +7597,39 @@
       <c r="A136" s="68">
         <v>92</v>
       </c>
-      <c r="B136" s="66" t="s">
+      <c r="B136" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="C136" s="66" t="s">
+      <c r="C136" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D136" s="66" t="s">
+      <c r="D136" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E136" s="66" t="s">
+      <c r="E136" s="69" t="s">
         <v>20</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="G136" s="69">
+      <c r="G136" s="70">
         <v>46118</v>
       </c>
-      <c r="H136" s="71" t="s">
+      <c r="H136" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="I136" s="71" t="s">
+      <c r="I136" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J136" s="66" t="s">
+      <c r="J136" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="K136" s="66"/>
+      <c r="K136" s="69"/>
       <c r="L136" s="65"/>
       <c r="M136" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="N136" s="66"/>
+      <c r="N136" s="69"/>
       <c r="O136" s="65" t="s">
         <v>63</v>
       </c>
@@ -7635,52 +7638,52 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A137" s="68"/>
-      <c r="B137" s="66"/>
-      <c r="C137" s="66"/>
-      <c r="D137" s="66"/>
-      <c r="E137" s="66"/>
+      <c r="B137" s="69"/>
+      <c r="C137" s="69"/>
+      <c r="D137" s="69"/>
+      <c r="E137" s="69"/>
       <c r="F137" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="G137" s="69"/>
-      <c r="H137" s="71"/>
-      <c r="I137" s="71"/>
-      <c r="J137" s="66"/>
-      <c r="K137" s="66"/>
+      <c r="G137" s="70"/>
+      <c r="H137" s="67"/>
+      <c r="I137" s="67"/>
+      <c r="J137" s="69"/>
+      <c r="K137" s="69"/>
       <c r="L137" s="65"/>
       <c r="M137" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="N137" s="66"/>
+      <c r="N137" s="69"/>
       <c r="O137" s="65"/>
       <c r="P137" s="65"/>
       <c r="Q137" s="65"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A138" s="68"/>
-      <c r="B138" s="66"/>
-      <c r="C138" s="66"/>
-      <c r="D138" s="66"/>
-      <c r="E138" s="66"/>
+      <c r="B138" s="69"/>
+      <c r="C138" s="69"/>
+      <c r="D138" s="69"/>
+      <c r="E138" s="69"/>
       <c r="F138" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="G138" s="69"/>
-      <c r="H138" s="71"/>
-      <c r="I138" s="71"/>
-      <c r="J138" s="66"/>
-      <c r="K138" s="66"/>
+      <c r="G138" s="70"/>
+      <c r="H138" s="67"/>
+      <c r="I138" s="67"/>
+      <c r="J138" s="69"/>
+      <c r="K138" s="69"/>
       <c r="L138" s="65"/>
       <c r="M138" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="N138" s="66"/>
+      <c r="N138" s="69"/>
       <c r="O138" s="65"/>
       <c r="P138" s="65"/>
       <c r="Q138" s="65"/>
     </row>
     <row r="139" spans="1:17" ht="114" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A139" s="76">
+      <c r="A139" s="78">
         <v>93</v>
       </c>
       <c r="B139" s="74" t="s">
@@ -7689,32 +7692,32 @@
       <c r="C139" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="D139" s="66"/>
+      <c r="D139" s="69"/>
       <c r="E139" s="74" t="s">
         <v>29</v>
       </c>
       <c r="F139" s="50" t="s">
         <v>302</v>
       </c>
-      <c r="G139" s="77">
+      <c r="G139" s="75">
         <v>46118</v>
       </c>
-      <c r="H139" s="73" t="s">
+      <c r="H139" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="I139" s="73" t="s">
+      <c r="I139" s="76" t="s">
         <v>23</v>
       </c>
       <c r="J139" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="K139" s="66"/>
+      <c r="K139" s="69"/>
       <c r="L139" s="65"/>
-      <c r="M139" s="75" t="s">
+      <c r="M139" s="79" t="s">
         <v>303</v>
       </c>
-      <c r="N139" s="66"/>
-      <c r="O139" s="72" t="s">
+      <c r="N139" s="69"/>
+      <c r="O139" s="77" t="s">
         <v>59</v>
       </c>
       <c r="P139" s="65"/>
@@ -7723,23 +7726,23 @@
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A140" s="76"/>
+      <c r="A140" s="78"/>
       <c r="B140" s="74"/>
       <c r="C140" s="74"/>
-      <c r="D140" s="66"/>
+      <c r="D140" s="69"/>
       <c r="E140" s="74"/>
       <c r="F140" s="51" t="s">
         <v>292</v>
       </c>
-      <c r="G140" s="77"/>
-      <c r="H140" s="73"/>
-      <c r="I140" s="73"/>
+      <c r="G140" s="75"/>
+      <c r="H140" s="76"/>
+      <c r="I140" s="76"/>
       <c r="J140" s="74"/>
-      <c r="K140" s="66"/>
+      <c r="K140" s="69"/>
       <c r="L140" s="65"/>
-      <c r="M140" s="75"/>
-      <c r="N140" s="66"/>
-      <c r="O140" s="72"/>
+      <c r="M140" s="79"/>
+      <c r="N140" s="69"/>
+      <c r="O140" s="77"/>
       <c r="P140" s="65"/>
       <c r="Q140" s="65"/>
     </row>
@@ -7747,41 +7750,41 @@
       <c r="A141" s="68">
         <v>94</v>
       </c>
-      <c r="B141" s="66" t="s">
+      <c r="B141" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="C141" s="66" t="s">
+      <c r="C141" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D141" s="66" t="s">
+      <c r="D141" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E141" s="66" t="s">
+      <c r="E141" s="69" t="s">
         <v>20</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="G141" s="69">
+      <c r="G141" s="70">
         <v>46118</v>
       </c>
-      <c r="H141" s="71" t="s">
+      <c r="H141" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="I141" s="71" t="s">
+      <c r="I141" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J141" s="66" t="s">
+      <c r="J141" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K141" s="66" t="s">
+      <c r="K141" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L141" s="65"/>
-      <c r="M141" s="67" t="s">
+      <c r="M141" s="66" t="s">
         <v>306</v>
       </c>
-      <c r="N141" s="66"/>
+      <c r="N141" s="69"/>
       <c r="O141" s="65" t="s">
         <v>111</v>
       </c>
@@ -7790,21 +7793,21 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A142" s="68"/>
-      <c r="B142" s="66"/>
-      <c r="C142" s="66"/>
-      <c r="D142" s="66"/>
-      <c r="E142" s="66"/>
+      <c r="B142" s="69"/>
+      <c r="C142" s="69"/>
+      <c r="D142" s="69"/>
+      <c r="E142" s="69"/>
       <c r="F142" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="G142" s="69"/>
-      <c r="H142" s="71"/>
-      <c r="I142" s="71"/>
-      <c r="J142" s="66"/>
-      <c r="K142" s="66"/>
+      <c r="G142" s="70"/>
+      <c r="H142" s="67"/>
+      <c r="I142" s="67"/>
+      <c r="J142" s="69"/>
+      <c r="K142" s="69"/>
       <c r="L142" s="65"/>
-      <c r="M142" s="67"/>
-      <c r="N142" s="66"/>
+      <c r="M142" s="66"/>
+      <c r="N142" s="69"/>
       <c r="O142" s="65"/>
       <c r="P142" s="65"/>
       <c r="Q142" s="65"/>
@@ -7850,37 +7853,37 @@
       <c r="A144" s="68">
         <v>96</v>
       </c>
-      <c r="B144" s="66" t="s">
+      <c r="B144" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="C144" s="66" t="s">
+      <c r="C144" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D144" s="66" t="s">
+      <c r="D144" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E144" s="66"/>
+      <c r="E144" s="69"/>
       <c r="F144" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="G144" s="69">
+      <c r="G144" s="70">
         <v>46118</v>
       </c>
-      <c r="H144" s="71" t="s">
+      <c r="H144" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="I144" s="71" t="s">
+      <c r="I144" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J144" s="66" t="s">
+      <c r="J144" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="K144" s="66"/>
+      <c r="K144" s="69"/>
       <c r="L144" s="65"/>
       <c r="M144" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="N144" s="66"/>
+      <c r="N144" s="69"/>
       <c r="O144" s="65" t="s">
         <v>48</v>
       </c>
@@ -7889,84 +7892,84 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A145" s="68"/>
-      <c r="B145" s="66"/>
-      <c r="C145" s="66"/>
-      <c r="D145" s="66"/>
-      <c r="E145" s="66"/>
+      <c r="B145" s="69"/>
+      <c r="C145" s="69"/>
+      <c r="D145" s="69"/>
+      <c r="E145" s="69"/>
       <c r="F145" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="G145" s="69"/>
-      <c r="H145" s="71"/>
-      <c r="I145" s="71"/>
-      <c r="J145" s="66"/>
-      <c r="K145" s="66"/>
+      <c r="G145" s="70"/>
+      <c r="H145" s="67"/>
+      <c r="I145" s="67"/>
+      <c r="J145" s="69"/>
+      <c r="K145" s="69"/>
       <c r="L145" s="65"/>
       <c r="M145" s="41"/>
-      <c r="N145" s="66"/>
+      <c r="N145" s="69"/>
       <c r="O145" s="65"/>
       <c r="P145" s="65"/>
       <c r="Q145" s="65"/>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A146" s="68"/>
-      <c r="B146" s="66"/>
-      <c r="C146" s="66"/>
-      <c r="D146" s="66"/>
-      <c r="E146" s="66"/>
+      <c r="B146" s="69"/>
+      <c r="C146" s="69"/>
+      <c r="D146" s="69"/>
+      <c r="E146" s="69"/>
       <c r="F146" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="G146" s="69"/>
-      <c r="H146" s="71"/>
-      <c r="I146" s="71"/>
-      <c r="J146" s="66"/>
-      <c r="K146" s="66"/>
+      <c r="G146" s="70"/>
+      <c r="H146" s="67"/>
+      <c r="I146" s="67"/>
+      <c r="J146" s="69"/>
+      <c r="K146" s="69"/>
       <c r="L146" s="65"/>
       <c r="M146" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="N146" s="66"/>
+      <c r="N146" s="69"/>
       <c r="O146" s="65"/>
       <c r="P146" s="65"/>
       <c r="Q146" s="65"/>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A147" s="68"/>
-      <c r="B147" s="66"/>
-      <c r="C147" s="66"/>
-      <c r="D147" s="66"/>
-      <c r="E147" s="66"/>
+      <c r="B147" s="69"/>
+      <c r="C147" s="69"/>
+      <c r="D147" s="69"/>
+      <c r="E147" s="69"/>
       <c r="F147" s="11"/>
-      <c r="G147" s="69"/>
-      <c r="H147" s="71"/>
-      <c r="I147" s="71"/>
-      <c r="J147" s="66"/>
-      <c r="K147" s="66"/>
+      <c r="G147" s="70"/>
+      <c r="H147" s="67"/>
+      <c r="I147" s="67"/>
+      <c r="J147" s="69"/>
+      <c r="K147" s="69"/>
       <c r="L147" s="65"/>
       <c r="M147" s="16"/>
-      <c r="N147" s="66"/>
+      <c r="N147" s="69"/>
       <c r="O147" s="65"/>
       <c r="P147" s="65"/>
       <c r="Q147" s="65"/>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A148" s="68"/>
-      <c r="B148" s="66"/>
-      <c r="C148" s="66"/>
-      <c r="D148" s="66"/>
-      <c r="E148" s="66"/>
+      <c r="B148" s="69"/>
+      <c r="C148" s="69"/>
+      <c r="D148" s="69"/>
+      <c r="E148" s="69"/>
       <c r="F148" s="11"/>
-      <c r="G148" s="69"/>
-      <c r="H148" s="71"/>
-      <c r="I148" s="71"/>
-      <c r="J148" s="66"/>
-      <c r="K148" s="66"/>
+      <c r="G148" s="70"/>
+      <c r="H148" s="67"/>
+      <c r="I148" s="67"/>
+      <c r="J148" s="69"/>
+      <c r="K148" s="69"/>
       <c r="L148" s="65"/>
       <c r="M148" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="N148" s="66"/>
+      <c r="N148" s="69"/>
       <c r="O148" s="65"/>
       <c r="P148" s="65"/>
       <c r="Q148" s="65"/>
@@ -7975,35 +7978,35 @@
       <c r="A149" s="68">
         <v>97</v>
       </c>
-      <c r="B149" s="66" t="s">
+      <c r="B149" s="69" t="s">
         <v>315</v>
       </c>
-      <c r="C149" s="66" t="s">
+      <c r="C149" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D149" s="66" t="s">
+      <c r="D149" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E149" s="66"/>
+      <c r="E149" s="69"/>
       <c r="F149" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="G149" s="69">
+      <c r="G149" s="70">
         <v>46118</v>
       </c>
-      <c r="H149" s="71" t="s">
+      <c r="H149" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="I149" s="71"/>
-      <c r="J149" s="66" t="s">
+      <c r="I149" s="67"/>
+      <c r="J149" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="K149" s="66"/>
+      <c r="K149" s="69"/>
       <c r="L149" s="65"/>
-      <c r="M149" s="67" t="s">
+      <c r="M149" s="66" t="s">
         <v>332</v>
       </c>
-      <c r="N149" s="66"/>
+      <c r="N149" s="69"/>
       <c r="O149" s="65" t="s">
         <v>73</v>
       </c>
@@ -8012,391 +8015,391 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A150" s="68"/>
-      <c r="B150" s="66"/>
-      <c r="C150" s="66"/>
-      <c r="D150" s="66"/>
-      <c r="E150" s="66"/>
+      <c r="B150" s="69"/>
+      <c r="C150" s="69"/>
+      <c r="D150" s="69"/>
+      <c r="E150" s="69"/>
       <c r="F150" s="27"/>
-      <c r="G150" s="69"/>
-      <c r="H150" s="71"/>
-      <c r="I150" s="71"/>
-      <c r="J150" s="66"/>
-      <c r="K150" s="66"/>
+      <c r="G150" s="70"/>
+      <c r="H150" s="67"/>
+      <c r="I150" s="67"/>
+      <c r="J150" s="69"/>
+      <c r="K150" s="69"/>
       <c r="L150" s="65"/>
-      <c r="M150" s="67"/>
-      <c r="N150" s="66"/>
+      <c r="M150" s="66"/>
+      <c r="N150" s="69"/>
       <c r="O150" s="65"/>
       <c r="P150" s="65"/>
       <c r="Q150" s="65"/>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A151" s="68"/>
-      <c r="B151" s="66"/>
-      <c r="C151" s="66"/>
-      <c r="D151" s="66"/>
-      <c r="E151" s="66"/>
+      <c r="B151" s="69"/>
+      <c r="C151" s="69"/>
+      <c r="D151" s="69"/>
+      <c r="E151" s="69"/>
       <c r="F151" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="G151" s="69"/>
-      <c r="H151" s="71"/>
-      <c r="I151" s="71"/>
-      <c r="J151" s="66"/>
-      <c r="K151" s="66"/>
+      <c r="G151" s="70"/>
+      <c r="H151" s="67"/>
+      <c r="I151" s="67"/>
+      <c r="J151" s="69"/>
+      <c r="K151" s="69"/>
       <c r="L151" s="65"/>
-      <c r="M151" s="67"/>
-      <c r="N151" s="66"/>
+      <c r="M151" s="66"/>
+      <c r="N151" s="69"/>
       <c r="O151" s="65"/>
       <c r="P151" s="65"/>
       <c r="Q151" s="65"/>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A152" s="68"/>
-      <c r="B152" s="66"/>
-      <c r="C152" s="66"/>
-      <c r="D152" s="66"/>
-      <c r="E152" s="66"/>
+      <c r="B152" s="69"/>
+      <c r="C152" s="69"/>
+      <c r="D152" s="69"/>
+      <c r="E152" s="69"/>
       <c r="F152" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="G152" s="69"/>
-      <c r="H152" s="71"/>
-      <c r="I152" s="71"/>
-      <c r="J152" s="66"/>
-      <c r="K152" s="66"/>
+      <c r="G152" s="70"/>
+      <c r="H152" s="67"/>
+      <c r="I152" s="67"/>
+      <c r="J152" s="69"/>
+      <c r="K152" s="69"/>
       <c r="L152" s="65"/>
-      <c r="M152" s="67"/>
-      <c r="N152" s="66"/>
+      <c r="M152" s="66"/>
+      <c r="N152" s="69"/>
       <c r="O152" s="65"/>
       <c r="P152" s="65"/>
       <c r="Q152" s="65"/>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A153" s="68"/>
-      <c r="B153" s="66"/>
-      <c r="C153" s="66"/>
-      <c r="D153" s="66"/>
-      <c r="E153" s="66"/>
+      <c r="B153" s="69"/>
+      <c r="C153" s="69"/>
+      <c r="D153" s="69"/>
+      <c r="E153" s="69"/>
       <c r="F153" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="G153" s="69"/>
-      <c r="H153" s="71"/>
-      <c r="I153" s="71"/>
-      <c r="J153" s="66"/>
-      <c r="K153" s="66"/>
+      <c r="G153" s="70"/>
+      <c r="H153" s="67"/>
+      <c r="I153" s="67"/>
+      <c r="J153" s="69"/>
+      <c r="K153" s="69"/>
       <c r="L153" s="65"/>
-      <c r="M153" s="67"/>
-      <c r="N153" s="66"/>
+      <c r="M153" s="66"/>
+      <c r="N153" s="69"/>
       <c r="O153" s="65"/>
       <c r="P153" s="65"/>
       <c r="Q153" s="65"/>
     </row>
     <row r="154" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A154" s="68"/>
-      <c r="B154" s="66"/>
-      <c r="C154" s="66"/>
-      <c r="D154" s="66"/>
-      <c r="E154" s="66"/>
+      <c r="B154" s="69"/>
+      <c r="C154" s="69"/>
+      <c r="D154" s="69"/>
+      <c r="E154" s="69"/>
       <c r="F154" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="G154" s="69"/>
-      <c r="H154" s="71"/>
-      <c r="I154" s="71"/>
-      <c r="J154" s="66"/>
-      <c r="K154" s="66"/>
+      <c r="G154" s="70"/>
+      <c r="H154" s="67"/>
+      <c r="I154" s="67"/>
+      <c r="J154" s="69"/>
+      <c r="K154" s="69"/>
       <c r="L154" s="65"/>
-      <c r="M154" s="67"/>
-      <c r="N154" s="66"/>
+      <c r="M154" s="66"/>
+      <c r="N154" s="69"/>
       <c r="O154" s="65"/>
       <c r="P154" s="65"/>
       <c r="Q154" s="65"/>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A155" s="68"/>
-      <c r="B155" s="66"/>
-      <c r="C155" s="66"/>
-      <c r="D155" s="66"/>
-      <c r="E155" s="66"/>
+      <c r="B155" s="69"/>
+      <c r="C155" s="69"/>
+      <c r="D155" s="69"/>
+      <c r="E155" s="69"/>
       <c r="F155" s="27"/>
-      <c r="G155" s="69"/>
-      <c r="H155" s="71"/>
-      <c r="I155" s="71"/>
-      <c r="J155" s="66"/>
-      <c r="K155" s="66"/>
+      <c r="G155" s="70"/>
+      <c r="H155" s="67"/>
+      <c r="I155" s="67"/>
+      <c r="J155" s="69"/>
+      <c r="K155" s="69"/>
       <c r="L155" s="65"/>
-      <c r="M155" s="67"/>
-      <c r="N155" s="66"/>
+      <c r="M155" s="66"/>
+      <c r="N155" s="69"/>
       <c r="O155" s="65"/>
       <c r="P155" s="65"/>
       <c r="Q155" s="65"/>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A156" s="68"/>
-      <c r="B156" s="66"/>
-      <c r="C156" s="66"/>
-      <c r="D156" s="66"/>
-      <c r="E156" s="66"/>
+      <c r="B156" s="69"/>
+      <c r="C156" s="69"/>
+      <c r="D156" s="69"/>
+      <c r="E156" s="69"/>
       <c r="F156" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="G156" s="69"/>
-      <c r="H156" s="71"/>
-      <c r="I156" s="71"/>
-      <c r="J156" s="66"/>
-      <c r="K156" s="66"/>
+      <c r="G156" s="70"/>
+      <c r="H156" s="67"/>
+      <c r="I156" s="67"/>
+      <c r="J156" s="69"/>
+      <c r="K156" s="69"/>
       <c r="L156" s="65"/>
-      <c r="M156" s="67"/>
-      <c r="N156" s="66"/>
+      <c r="M156" s="66"/>
+      <c r="N156" s="69"/>
       <c r="O156" s="65"/>
       <c r="P156" s="65"/>
       <c r="Q156" s="65"/>
     </row>
     <row r="157" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A157" s="68"/>
-      <c r="B157" s="66"/>
-      <c r="C157" s="66"/>
-      <c r="D157" s="66"/>
-      <c r="E157" s="66"/>
+      <c r="B157" s="69"/>
+      <c r="C157" s="69"/>
+      <c r="D157" s="69"/>
+      <c r="E157" s="69"/>
       <c r="F157" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="G157" s="69"/>
-      <c r="H157" s="71"/>
-      <c r="I157" s="71"/>
-      <c r="J157" s="66"/>
-      <c r="K157" s="66"/>
+      <c r="G157" s="70"/>
+      <c r="H157" s="67"/>
+      <c r="I157" s="67"/>
+      <c r="J157" s="69"/>
+      <c r="K157" s="69"/>
       <c r="L157" s="65"/>
-      <c r="M157" s="67"/>
-      <c r="N157" s="66"/>
+      <c r="M157" s="66"/>
+      <c r="N157" s="69"/>
       <c r="O157" s="65"/>
       <c r="P157" s="65"/>
       <c r="Q157" s="65"/>
     </row>
     <row r="158" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A158" s="68"/>
-      <c r="B158" s="66"/>
-      <c r="C158" s="66"/>
-      <c r="D158" s="66"/>
-      <c r="E158" s="66"/>
+      <c r="B158" s="69"/>
+      <c r="C158" s="69"/>
+      <c r="D158" s="69"/>
+      <c r="E158" s="69"/>
       <c r="F158" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="G158" s="69"/>
-      <c r="H158" s="71"/>
-      <c r="I158" s="71"/>
-      <c r="J158" s="66"/>
-      <c r="K158" s="66"/>
+      <c r="G158" s="70"/>
+      <c r="H158" s="67"/>
+      <c r="I158" s="67"/>
+      <c r="J158" s="69"/>
+      <c r="K158" s="69"/>
       <c r="L158" s="65"/>
-      <c r="M158" s="67"/>
-      <c r="N158" s="66"/>
+      <c r="M158" s="66"/>
+      <c r="N158" s="69"/>
       <c r="O158" s="65"/>
       <c r="P158" s="65"/>
       <c r="Q158" s="65"/>
     </row>
     <row r="159" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A159" s="68"/>
-      <c r="B159" s="66"/>
-      <c r="C159" s="66"/>
-      <c r="D159" s="66"/>
-      <c r="E159" s="66"/>
+      <c r="B159" s="69"/>
+      <c r="C159" s="69"/>
+      <c r="D159" s="69"/>
+      <c r="E159" s="69"/>
       <c r="F159" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="G159" s="69"/>
-      <c r="H159" s="71"/>
-      <c r="I159" s="71"/>
-      <c r="J159" s="66"/>
-      <c r="K159" s="66"/>
+      <c r="G159" s="70"/>
+      <c r="H159" s="67"/>
+      <c r="I159" s="67"/>
+      <c r="J159" s="69"/>
+      <c r="K159" s="69"/>
       <c r="L159" s="65"/>
-      <c r="M159" s="67"/>
-      <c r="N159" s="66"/>
+      <c r="M159" s="66"/>
+      <c r="N159" s="69"/>
       <c r="O159" s="65"/>
       <c r="P159" s="65"/>
       <c r="Q159" s="65"/>
     </row>
     <row r="160" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A160" s="68"/>
-      <c r="B160" s="66"/>
-      <c r="C160" s="66"/>
-      <c r="D160" s="66"/>
-      <c r="E160" s="66"/>
+      <c r="B160" s="69"/>
+      <c r="C160" s="69"/>
+      <c r="D160" s="69"/>
+      <c r="E160" s="69"/>
       <c r="F160" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="G160" s="69"/>
-      <c r="H160" s="71"/>
-      <c r="I160" s="71"/>
-      <c r="J160" s="66"/>
-      <c r="K160" s="66"/>
+      <c r="G160" s="70"/>
+      <c r="H160" s="67"/>
+      <c r="I160" s="67"/>
+      <c r="J160" s="69"/>
+      <c r="K160" s="69"/>
       <c r="L160" s="65"/>
-      <c r="M160" s="67"/>
-      <c r="N160" s="66"/>
+      <c r="M160" s="66"/>
+      <c r="N160" s="69"/>
       <c r="O160" s="65"/>
       <c r="P160" s="65"/>
       <c r="Q160" s="65"/>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A161" s="68"/>
-      <c r="B161" s="66"/>
-      <c r="C161" s="66"/>
-      <c r="D161" s="66"/>
-      <c r="E161" s="66"/>
+      <c r="B161" s="69"/>
+      <c r="C161" s="69"/>
+      <c r="D161" s="69"/>
+      <c r="E161" s="69"/>
       <c r="F161" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="G161" s="69"/>
-      <c r="H161" s="71"/>
-      <c r="I161" s="71"/>
-      <c r="J161" s="66"/>
-      <c r="K161" s="66"/>
+      <c r="G161" s="70"/>
+      <c r="H161" s="67"/>
+      <c r="I161" s="67"/>
+      <c r="J161" s="69"/>
+      <c r="K161" s="69"/>
       <c r="L161" s="65"/>
-      <c r="M161" s="67"/>
-      <c r="N161" s="66"/>
+      <c r="M161" s="66"/>
+      <c r="N161" s="69"/>
       <c r="O161" s="65"/>
       <c r="P161" s="65"/>
       <c r="Q161" s="65"/>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A162" s="68"/>
-      <c r="B162" s="66"/>
-      <c r="C162" s="66"/>
-      <c r="D162" s="66"/>
-      <c r="E162" s="66"/>
+      <c r="B162" s="69"/>
+      <c r="C162" s="69"/>
+      <c r="D162" s="69"/>
+      <c r="E162" s="69"/>
       <c r="F162" s="27"/>
-      <c r="G162" s="69"/>
-      <c r="H162" s="71"/>
-      <c r="I162" s="71"/>
-      <c r="J162" s="66"/>
-      <c r="K162" s="66"/>
+      <c r="G162" s="70"/>
+      <c r="H162" s="67"/>
+      <c r="I162" s="67"/>
+      <c r="J162" s="69"/>
+      <c r="K162" s="69"/>
       <c r="L162" s="65"/>
-      <c r="M162" s="67"/>
-      <c r="N162" s="66"/>
+      <c r="M162" s="66"/>
+      <c r="N162" s="69"/>
       <c r="O162" s="65"/>
       <c r="P162" s="65"/>
       <c r="Q162" s="65"/>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A163" s="68"/>
-      <c r="B163" s="66"/>
-      <c r="C163" s="66"/>
-      <c r="D163" s="66"/>
-      <c r="E163" s="66"/>
+      <c r="B163" s="69"/>
+      <c r="C163" s="69"/>
+      <c r="D163" s="69"/>
+      <c r="E163" s="69"/>
       <c r="F163" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="G163" s="69"/>
-      <c r="H163" s="71"/>
-      <c r="I163" s="71"/>
-      <c r="J163" s="66"/>
-      <c r="K163" s="66"/>
+      <c r="G163" s="70"/>
+      <c r="H163" s="67"/>
+      <c r="I163" s="67"/>
+      <c r="J163" s="69"/>
+      <c r="K163" s="69"/>
       <c r="L163" s="65"/>
-      <c r="M163" s="67"/>
-      <c r="N163" s="66"/>
+      <c r="M163" s="66"/>
+      <c r="N163" s="69"/>
       <c r="O163" s="65"/>
       <c r="P163" s="65"/>
       <c r="Q163" s="65"/>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A164" s="68"/>
-      <c r="B164" s="66"/>
-      <c r="C164" s="66"/>
-      <c r="D164" s="66"/>
-      <c r="E164" s="66"/>
+      <c r="B164" s="69"/>
+      <c r="C164" s="69"/>
+      <c r="D164" s="69"/>
+      <c r="E164" s="69"/>
       <c r="F164" s="27"/>
-      <c r="G164" s="69"/>
-      <c r="H164" s="71"/>
-      <c r="I164" s="71"/>
-      <c r="J164" s="66"/>
-      <c r="K164" s="66"/>
+      <c r="G164" s="70"/>
+      <c r="H164" s="67"/>
+      <c r="I164" s="67"/>
+      <c r="J164" s="69"/>
+      <c r="K164" s="69"/>
       <c r="L164" s="65"/>
-      <c r="M164" s="67"/>
-      <c r="N164" s="66"/>
+      <c r="M164" s="66"/>
+      <c r="N164" s="69"/>
       <c r="O164" s="65"/>
       <c r="P164" s="65"/>
       <c r="Q164" s="65"/>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A165" s="68"/>
-      <c r="B165" s="66"/>
-      <c r="C165" s="66"/>
-      <c r="D165" s="66"/>
-      <c r="E165" s="66"/>
+      <c r="B165" s="69"/>
+      <c r="C165" s="69"/>
+      <c r="D165" s="69"/>
+      <c r="E165" s="69"/>
       <c r="F165" s="32" t="s">
         <v>328</v>
       </c>
-      <c r="G165" s="69"/>
-      <c r="H165" s="71"/>
-      <c r="I165" s="71"/>
-      <c r="J165" s="66"/>
-      <c r="K165" s="66"/>
+      <c r="G165" s="70"/>
+      <c r="H165" s="67"/>
+      <c r="I165" s="67"/>
+      <c r="J165" s="69"/>
+      <c r="K165" s="69"/>
       <c r="L165" s="65"/>
-      <c r="M165" s="67"/>
-      <c r="N165" s="66"/>
+      <c r="M165" s="66"/>
+      <c r="N165" s="69"/>
       <c r="O165" s="65"/>
       <c r="P165" s="65"/>
       <c r="Q165" s="65"/>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A166" s="68"/>
-      <c r="B166" s="66"/>
-      <c r="C166" s="66"/>
-      <c r="D166" s="66"/>
-      <c r="E166" s="66"/>
+      <c r="B166" s="69"/>
+      <c r="C166" s="69"/>
+      <c r="D166" s="69"/>
+      <c r="E166" s="69"/>
       <c r="F166" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="G166" s="69"/>
-      <c r="H166" s="71"/>
-      <c r="I166" s="71"/>
-      <c r="J166" s="66"/>
-      <c r="K166" s="66"/>
+      <c r="G166" s="70"/>
+      <c r="H166" s="67"/>
+      <c r="I166" s="67"/>
+      <c r="J166" s="69"/>
+      <c r="K166" s="69"/>
       <c r="L166" s="65"/>
-      <c r="M166" s="67"/>
-      <c r="N166" s="66"/>
+      <c r="M166" s="66"/>
+      <c r="N166" s="69"/>
       <c r="O166" s="65"/>
       <c r="P166" s="65"/>
       <c r="Q166" s="65"/>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A167" s="68"/>
-      <c r="B167" s="66"/>
-      <c r="C167" s="66"/>
-      <c r="D167" s="66"/>
-      <c r="E167" s="66"/>
+      <c r="B167" s="69"/>
+      <c r="C167" s="69"/>
+      <c r="D167" s="69"/>
+      <c r="E167" s="69"/>
       <c r="F167" s="32" t="s">
         <v>330</v>
       </c>
-      <c r="G167" s="69"/>
-      <c r="H167" s="71"/>
-      <c r="I167" s="71"/>
-      <c r="J167" s="66"/>
-      <c r="K167" s="66"/>
+      <c r="G167" s="70"/>
+      <c r="H167" s="67"/>
+      <c r="I167" s="67"/>
+      <c r="J167" s="69"/>
+      <c r="K167" s="69"/>
       <c r="L167" s="65"/>
-      <c r="M167" s="67"/>
-      <c r="N167" s="66"/>
+      <c r="M167" s="66"/>
+      <c r="N167" s="69"/>
       <c r="O167" s="65"/>
       <c r="P167" s="65"/>
       <c r="Q167" s="65"/>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A168" s="68"/>
-      <c r="B168" s="66"/>
-      <c r="C168" s="66"/>
-      <c r="D168" s="66"/>
-      <c r="E168" s="66"/>
+      <c r="B168" s="69"/>
+      <c r="C168" s="69"/>
+      <c r="D168" s="69"/>
+      <c r="E168" s="69"/>
       <c r="F168" s="32" t="s">
         <v>331</v>
       </c>
-      <c r="G168" s="69"/>
-      <c r="H168" s="71"/>
-      <c r="I168" s="71"/>
-      <c r="J168" s="66"/>
-      <c r="K168" s="66"/>
+      <c r="G168" s="70"/>
+      <c r="H168" s="67"/>
+      <c r="I168" s="67"/>
+      <c r="J168" s="69"/>
+      <c r="K168" s="69"/>
       <c r="L168" s="65"/>
-      <c r="M168" s="67"/>
-      <c r="N168" s="66"/>
+      <c r="M168" s="66"/>
+      <c r="N168" s="69"/>
       <c r="O168" s="65"/>
       <c r="P168" s="65"/>
       <c r="Q168" s="65"/>
@@ -8405,39 +8408,39 @@
       <c r="A169" s="68">
         <v>98</v>
       </c>
-      <c r="B169" s="66" t="s">
+      <c r="B169" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="C169" s="66" t="s">
+      <c r="C169" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D169" s="66" t="s">
+      <c r="D169" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E169" s="67"/>
+      <c r="E169" s="66"/>
       <c r="F169" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="G169" s="69">
+      <c r="G169" s="70">
         <v>46119</v>
       </c>
-      <c r="H169" s="71" t="s">
+      <c r="H169" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="I169" s="71" t="s">
+      <c r="I169" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J169" s="66" t="s">
+      <c r="J169" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K169" s="66" t="s">
+      <c r="K169" s="69" t="s">
         <v>24</v>
       </c>
       <c r="L169" s="65"/>
-      <c r="M169" s="67" t="s">
+      <c r="M169" s="66" t="s">
         <v>334</v>
       </c>
-      <c r="N169" s="66"/>
+      <c r="N169" s="69"/>
       <c r="O169" s="65" t="s">
         <v>335</v>
       </c>
@@ -8446,21 +8449,21 @@
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A170" s="68"/>
-      <c r="B170" s="66"/>
-      <c r="C170" s="66"/>
-      <c r="D170" s="66"/>
-      <c r="E170" s="67"/>
+      <c r="B170" s="69"/>
+      <c r="C170" s="69"/>
+      <c r="D170" s="69"/>
+      <c r="E170" s="66"/>
       <c r="F170" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="G170" s="69"/>
-      <c r="H170" s="71"/>
-      <c r="I170" s="71"/>
-      <c r="J170" s="66"/>
-      <c r="K170" s="66"/>
+      <c r="G170" s="70"/>
+      <c r="H170" s="67"/>
+      <c r="I170" s="67"/>
+      <c r="J170" s="69"/>
+      <c r="K170" s="69"/>
       <c r="L170" s="65"/>
-      <c r="M170" s="67"/>
-      <c r="N170" s="66"/>
+      <c r="M170" s="66"/>
+      <c r="N170" s="69"/>
       <c r="O170" s="65"/>
       <c r="P170" s="65"/>
       <c r="Q170" s="65"/>
@@ -8764,35 +8767,35 @@
       <c r="A178" s="68">
         <v>106</v>
       </c>
-      <c r="B178" s="67" t="s">
+      <c r="B178" s="66" t="s">
         <v>352</v>
       </c>
-      <c r="C178" s="67" t="s">
+      <c r="C178" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D178" s="67" t="s">
+      <c r="D178" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E178" s="67" t="s">
+      <c r="E178" s="66" t="s">
         <v>20</v>
       </c>
       <c r="F178" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="G178" s="69">
+      <c r="G178" s="70">
         <v>46121</v>
       </c>
-      <c r="H178" s="70"/>
-      <c r="I178" s="71" t="s">
+      <c r="H178" s="73"/>
+      <c r="I178" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J178" s="66" t="s">
+      <c r="J178" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K178" s="66"/>
+      <c r="K178" s="69"/>
       <c r="L178" s="65"/>
-      <c r="M178" s="67"/>
-      <c r="N178" s="66"/>
+      <c r="M178" s="66"/>
+      <c r="N178" s="69"/>
       <c r="O178" s="65" t="s">
         <v>73</v>
       </c>
@@ -8801,21 +8804,21 @@
     </row>
     <row r="179" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A179" s="68"/>
-      <c r="B179" s="67"/>
-      <c r="C179" s="67"/>
-      <c r="D179" s="67"/>
-      <c r="E179" s="67"/>
+      <c r="B179" s="66"/>
+      <c r="C179" s="66"/>
+      <c r="D179" s="66"/>
+      <c r="E179" s="66"/>
       <c r="F179" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="G179" s="69"/>
-      <c r="H179" s="70"/>
-      <c r="I179" s="71"/>
-      <c r="J179" s="66"/>
-      <c r="K179" s="66"/>
+      <c r="G179" s="70"/>
+      <c r="H179" s="73"/>
+      <c r="I179" s="67"/>
+      <c r="J179" s="69"/>
+      <c r="K179" s="69"/>
       <c r="L179" s="65"/>
-      <c r="M179" s="67"/>
-      <c r="N179" s="66"/>
+      <c r="M179" s="66"/>
+      <c r="N179" s="69"/>
       <c r="O179" s="65"/>
       <c r="P179" s="65"/>
       <c r="Q179" s="65"/>
@@ -9193,35 +9196,35 @@
       <c r="A189" s="68">
         <v>116</v>
       </c>
-      <c r="B189" s="67" t="s">
+      <c r="B189" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="C189" s="67" t="s">
+      <c r="C189" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D189" s="67" t="s">
+      <c r="D189" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E189" s="67" t="s">
+      <c r="E189" s="66" t="s">
         <v>57</v>
       </c>
       <c r="F189" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="G189" s="69">
+      <c r="G189" s="70">
         <v>46126</v>
       </c>
-      <c r="H189" s="70" t="s">
+      <c r="H189" s="73" t="s">
         <v>380</v>
       </c>
       <c r="I189" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="J189" s="66"/>
-      <c r="K189" s="66"/>
+      <c r="J189" s="69"/>
+      <c r="K189" s="69"/>
       <c r="L189" s="65"/>
-      <c r="M189" s="67"/>
-      <c r="N189" s="66"/>
+      <c r="M189" s="66"/>
+      <c r="N189" s="69"/>
       <c r="O189" s="65" t="s">
         <v>381</v>
       </c>
@@ -9230,63 +9233,63 @@
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A190" s="68"/>
-      <c r="B190" s="67"/>
-      <c r="C190" s="67"/>
-      <c r="D190" s="67"/>
-      <c r="E190" s="67"/>
+      <c r="B190" s="66"/>
+      <c r="C190" s="66"/>
+      <c r="D190" s="66"/>
+      <c r="E190" s="66"/>
       <c r="F190" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="G190" s="69"/>
-      <c r="H190" s="70"/>
+      <c r="G190" s="70"/>
+      <c r="H190" s="73"/>
       <c r="I190" s="65"/>
-      <c r="J190" s="66"/>
-      <c r="K190" s="66"/>
+      <c r="J190" s="69"/>
+      <c r="K190" s="69"/>
       <c r="L190" s="65"/>
-      <c r="M190" s="67"/>
-      <c r="N190" s="66"/>
+      <c r="M190" s="66"/>
+      <c r="N190" s="69"/>
       <c r="O190" s="65"/>
       <c r="P190" s="65"/>
       <c r="Q190" s="65"/>
     </row>
     <row r="191" spans="1:17" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A191" s="68"/>
-      <c r="B191" s="67"/>
-      <c r="C191" s="67"/>
-      <c r="D191" s="67"/>
-      <c r="E191" s="67"/>
+      <c r="B191" s="66"/>
+      <c r="C191" s="66"/>
+      <c r="D191" s="66"/>
+      <c r="E191" s="66"/>
       <c r="F191" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="G191" s="69"/>
-      <c r="H191" s="70"/>
+      <c r="G191" s="70"/>
+      <c r="H191" s="73"/>
       <c r="I191" s="65"/>
-      <c r="J191" s="66"/>
-      <c r="K191" s="66"/>
+      <c r="J191" s="69"/>
+      <c r="K191" s="69"/>
       <c r="L191" s="65"/>
-      <c r="M191" s="67"/>
-      <c r="N191" s="66"/>
+      <c r="M191" s="66"/>
+      <c r="N191" s="69"/>
       <c r="O191" s="65"/>
       <c r="P191" s="65"/>
       <c r="Q191" s="65"/>
     </row>
     <row r="192" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A192" s="68"/>
-      <c r="B192" s="67"/>
-      <c r="C192" s="67"/>
-      <c r="D192" s="67"/>
-      <c r="E192" s="67"/>
+      <c r="B192" s="66"/>
+      <c r="C192" s="66"/>
+      <c r="D192" s="66"/>
+      <c r="E192" s="66"/>
       <c r="F192" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="G192" s="69"/>
-      <c r="H192" s="70"/>
+      <c r="G192" s="70"/>
+      <c r="H192" s="73"/>
       <c r="I192" s="65"/>
-      <c r="J192" s="66"/>
-      <c r="K192" s="66"/>
+      <c r="J192" s="69"/>
+      <c r="K192" s="69"/>
       <c r="L192" s="65"/>
-      <c r="M192" s="67"/>
-      <c r="N192" s="66"/>
+      <c r="M192" s="66"/>
+      <c r="N192" s="69"/>
       <c r="O192" s="65"/>
       <c r="P192" s="65"/>
       <c r="Q192" s="65"/>
@@ -9529,33 +9532,33 @@
       <c r="A199" s="68">
         <v>123</v>
       </c>
-      <c r="B199" s="67" t="s">
+      <c r="B199" s="66" t="s">
         <v>395</v>
       </c>
-      <c r="C199" s="67" t="s">
+      <c r="C199" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D199" s="67" t="s">
+      <c r="D199" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="E199" s="67" t="s">
+      <c r="E199" s="66" t="s">
         <v>66</v>
       </c>
       <c r="F199" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="G199" s="69">
+      <c r="G199" s="70">
         <v>46127</v>
       </c>
-      <c r="H199" s="70" t="s">
+      <c r="H199" s="73" t="s">
         <v>144</v>
       </c>
       <c r="I199" s="65"/>
-      <c r="J199" s="66"/>
-      <c r="K199" s="66"/>
+      <c r="J199" s="69"/>
+      <c r="K199" s="69"/>
       <c r="L199" s="65"/>
-      <c r="M199" s="67"/>
-      <c r="N199" s="66"/>
+      <c r="M199" s="66"/>
+      <c r="N199" s="69"/>
       <c r="O199" s="65" t="s">
         <v>398</v>
       </c>
@@ -9564,21 +9567,21 @@
     </row>
     <row r="200" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A200" s="68"/>
-      <c r="B200" s="67"/>
-      <c r="C200" s="67"/>
-      <c r="D200" s="67"/>
-      <c r="E200" s="67"/>
+      <c r="B200" s="66"/>
+      <c r="C200" s="66"/>
+      <c r="D200" s="66"/>
+      <c r="E200" s="66"/>
       <c r="F200" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="G200" s="69"/>
-      <c r="H200" s="70"/>
+      <c r="G200" s="70"/>
+      <c r="H200" s="73"/>
       <c r="I200" s="65"/>
-      <c r="J200" s="66"/>
-      <c r="K200" s="66"/>
+      <c r="J200" s="69"/>
+      <c r="K200" s="69"/>
       <c r="L200" s="65"/>
-      <c r="M200" s="67"/>
-      <c r="N200" s="66"/>
+      <c r="M200" s="66"/>
+      <c r="N200" s="69"/>
       <c r="O200" s="65"/>
       <c r="P200" s="65"/>
       <c r="Q200" s="65"/>
@@ -9587,33 +9590,33 @@
       <c r="A201" s="68">
         <v>124</v>
       </c>
-      <c r="B201" s="67" t="s">
+      <c r="B201" s="66" t="s">
         <v>399</v>
       </c>
-      <c r="C201" s="67" t="s">
+      <c r="C201" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D201" s="67" t="s">
+      <c r="D201" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="E201" s="67" t="s">
+      <c r="E201" s="66" t="s">
         <v>66</v>
       </c>
       <c r="F201" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="G201" s="69">
+      <c r="G201" s="70">
         <v>46127</v>
       </c>
-      <c r="H201" s="70" t="s">
+      <c r="H201" s="73" t="s">
         <v>144</v>
       </c>
       <c r="I201" s="65"/>
-      <c r="J201" s="66"/>
-      <c r="K201" s="66"/>
+      <c r="J201" s="69"/>
+      <c r="K201" s="69"/>
       <c r="L201" s="65"/>
-      <c r="M201" s="67"/>
-      <c r="N201" s="66"/>
+      <c r="M201" s="66"/>
+      <c r="N201" s="69"/>
       <c r="O201" s="65" t="s">
         <v>398</v>
       </c>
@@ -9622,21 +9625,21 @@
     </row>
     <row r="202" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A202" s="68"/>
-      <c r="B202" s="67"/>
-      <c r="C202" s="67"/>
-      <c r="D202" s="67"/>
-      <c r="E202" s="67"/>
+      <c r="B202" s="66"/>
+      <c r="C202" s="66"/>
+      <c r="D202" s="66"/>
+      <c r="E202" s="66"/>
       <c r="F202" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="G202" s="69"/>
-      <c r="H202" s="70"/>
+      <c r="G202" s="70"/>
+      <c r="H202" s="73"/>
       <c r="I202" s="65"/>
-      <c r="J202" s="66"/>
-      <c r="K202" s="66"/>
+      <c r="J202" s="69"/>
+      <c r="K202" s="69"/>
       <c r="L202" s="65"/>
-      <c r="M202" s="67"/>
-      <c r="N202" s="66"/>
+      <c r="M202" s="66"/>
+      <c r="N202" s="69"/>
       <c r="O202" s="65"/>
       <c r="P202" s="65"/>
       <c r="Q202" s="65"/>
@@ -9645,33 +9648,33 @@
       <c r="A203" s="68">
         <v>125</v>
       </c>
-      <c r="B203" s="67" t="s">
+      <c r="B203" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="C203" s="67" t="s">
+      <c r="C203" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D203" s="67" t="s">
+      <c r="D203" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="E203" s="67" t="s">
+      <c r="E203" s="66" t="s">
         <v>66</v>
       </c>
       <c r="F203" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="G203" s="69">
+      <c r="G203" s="70">
         <v>46127</v>
       </c>
-      <c r="H203" s="70" t="s">
+      <c r="H203" s="73" t="s">
         <v>144</v>
       </c>
       <c r="I203" s="65"/>
-      <c r="J203" s="66"/>
-      <c r="K203" s="66"/>
+      <c r="J203" s="69"/>
+      <c r="K203" s="69"/>
       <c r="L203" s="65"/>
-      <c r="M203" s="67"/>
-      <c r="N203" s="66"/>
+      <c r="M203" s="66"/>
+      <c r="N203" s="69"/>
       <c r="O203" s="65" t="s">
         <v>398</v>
       </c>
@@ -9680,21 +9683,21 @@
     </row>
     <row r="204" spans="1:17" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A204" s="68"/>
-      <c r="B204" s="67"/>
-      <c r="C204" s="67"/>
-      <c r="D204" s="67"/>
-      <c r="E204" s="67"/>
+      <c r="B204" s="66"/>
+      <c r="C204" s="66"/>
+      <c r="D204" s="66"/>
+      <c r="E204" s="66"/>
       <c r="F204" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="G204" s="69"/>
-      <c r="H204" s="70"/>
+      <c r="G204" s="70"/>
+      <c r="H204" s="73"/>
       <c r="I204" s="65"/>
-      <c r="J204" s="66"/>
-      <c r="K204" s="66"/>
+      <c r="J204" s="69"/>
+      <c r="K204" s="69"/>
       <c r="L204" s="65"/>
-      <c r="M204" s="67"/>
-      <c r="N204" s="66"/>
+      <c r="M204" s="66"/>
+      <c r="N204" s="69"/>
       <c r="O204" s="65"/>
       <c r="P204" s="65"/>
       <c r="Q204" s="65"/>
@@ -9703,33 +9706,33 @@
       <c r="A205" s="68">
         <v>126</v>
       </c>
-      <c r="B205" s="67" t="s">
+      <c r="B205" s="66" t="s">
         <v>404</v>
       </c>
-      <c r="C205" s="67" t="s">
+      <c r="C205" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D205" s="67" t="s">
+      <c r="D205" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="E205" s="67" t="s">
+      <c r="E205" s="66" t="s">
         <v>66</v>
       </c>
       <c r="F205" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="G205" s="69">
+      <c r="G205" s="70">
         <v>46127</v>
       </c>
-      <c r="H205" s="70" t="s">
+      <c r="H205" s="73" t="s">
         <v>144</v>
       </c>
       <c r="I205" s="65"/>
-      <c r="J205" s="66"/>
-      <c r="K205" s="66"/>
+      <c r="J205" s="69"/>
+      <c r="K205" s="69"/>
       <c r="L205" s="65"/>
-      <c r="M205" s="67"/>
-      <c r="N205" s="66"/>
+      <c r="M205" s="66"/>
+      <c r="N205" s="69"/>
       <c r="O205" s="65" t="s">
         <v>398</v>
       </c>
@@ -9738,21 +9741,21 @@
     </row>
     <row r="206" spans="1:17" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A206" s="68"/>
-      <c r="B206" s="67"/>
-      <c r="C206" s="67"/>
-      <c r="D206" s="67"/>
-      <c r="E206" s="67"/>
+      <c r="B206" s="66"/>
+      <c r="C206" s="66"/>
+      <c r="D206" s="66"/>
+      <c r="E206" s="66"/>
       <c r="F206" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="G206" s="69"/>
-      <c r="H206" s="70"/>
+      <c r="G206" s="70"/>
+      <c r="H206" s="73"/>
       <c r="I206" s="65"/>
-      <c r="J206" s="66"/>
-      <c r="K206" s="66"/>
+      <c r="J206" s="69"/>
+      <c r="K206" s="69"/>
       <c r="L206" s="65"/>
-      <c r="M206" s="67"/>
-      <c r="N206" s="66"/>
+      <c r="M206" s="66"/>
+      <c r="N206" s="69"/>
       <c r="O206" s="65"/>
       <c r="P206" s="65"/>
       <c r="Q206" s="65"/>
@@ -9946,33 +9949,33 @@
       <c r="A212" s="68">
         <v>132</v>
       </c>
-      <c r="B212" s="67" t="s">
+      <c r="B212" s="66" t="s">
         <v>417</v>
       </c>
-      <c r="C212" s="67" t="s">
+      <c r="C212" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D212" s="67" t="s">
+      <c r="D212" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E212" s="67" t="s">
+      <c r="E212" s="66" t="s">
         <v>20</v>
       </c>
       <c r="F212" s="37" t="s">
         <v>418</v>
       </c>
-      <c r="G212" s="69">
+      <c r="G212" s="70">
         <v>46128</v>
       </c>
-      <c r="H212" s="70" t="s">
+      <c r="H212" s="73" t="s">
         <v>42</v>
       </c>
       <c r="I212" s="65"/>
-      <c r="J212" s="66"/>
-      <c r="K212" s="66"/>
+      <c r="J212" s="69"/>
+      <c r="K212" s="69"/>
       <c r="L212" s="65"/>
-      <c r="M212" s="67"/>
-      <c r="N212" s="66"/>
+      <c r="M212" s="66"/>
+      <c r="N212" s="69"/>
       <c r="O212" s="65" t="s">
         <v>102</v>
       </c>
@@ -9981,42 +9984,42 @@
     </row>
     <row r="213" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A213" s="68"/>
-      <c r="B213" s="67"/>
-      <c r="C213" s="67"/>
-      <c r="D213" s="67"/>
-      <c r="E213" s="67"/>
+      <c r="B213" s="66"/>
+      <c r="C213" s="66"/>
+      <c r="D213" s="66"/>
+      <c r="E213" s="66"/>
       <c r="F213" s="37" t="s">
         <v>419</v>
       </c>
-      <c r="G213" s="69"/>
-      <c r="H213" s="70"/>
+      <c r="G213" s="70"/>
+      <c r="H213" s="73"/>
       <c r="I213" s="65"/>
-      <c r="J213" s="66"/>
-      <c r="K213" s="66"/>
+      <c r="J213" s="69"/>
+      <c r="K213" s="69"/>
       <c r="L213" s="65"/>
-      <c r="M213" s="67"/>
-      <c r="N213" s="66"/>
+      <c r="M213" s="66"/>
+      <c r="N213" s="69"/>
       <c r="O213" s="65"/>
       <c r="P213" s="65"/>
       <c r="Q213" s="65"/>
     </row>
     <row r="214" spans="1:17" ht="57" x14ac:dyDescent="0.45">
       <c r="A214" s="68"/>
-      <c r="B214" s="67"/>
-      <c r="C214" s="67"/>
-      <c r="D214" s="67"/>
-      <c r="E214" s="67"/>
+      <c r="B214" s="66"/>
+      <c r="C214" s="66"/>
+      <c r="D214" s="66"/>
+      <c r="E214" s="66"/>
       <c r="F214" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="G214" s="69"/>
-      <c r="H214" s="70"/>
+      <c r="G214" s="70"/>
+      <c r="H214" s="73"/>
       <c r="I214" s="65"/>
-      <c r="J214" s="66"/>
-      <c r="K214" s="66"/>
+      <c r="J214" s="69"/>
+      <c r="K214" s="69"/>
       <c r="L214" s="65"/>
-      <c r="M214" s="67"/>
-      <c r="N214" s="66"/>
+      <c r="M214" s="66"/>
+      <c r="N214" s="69"/>
       <c r="O214" s="65"/>
       <c r="P214" s="65"/>
       <c r="Q214" s="65"/>
@@ -10220,35 +10223,35 @@
       <c r="A220" s="68">
         <v>138</v>
       </c>
-      <c r="B220" s="67" t="s">
+      <c r="B220" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="C220" s="67" t="s">
+      <c r="C220" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D220" s="67" t="s">
+      <c r="D220" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E220" s="67" t="s">
+      <c r="E220" s="66" t="s">
         <v>57</v>
       </c>
       <c r="F220" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="G220" s="69">
+      <c r="G220" s="70">
         <v>46129</v>
       </c>
-      <c r="H220" s="70" t="s">
+      <c r="H220" s="73" t="s">
         <v>425</v>
       </c>
       <c r="I220" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="J220" s="66"/>
-      <c r="K220" s="66"/>
+      <c r="J220" s="69"/>
+      <c r="K220" s="69"/>
       <c r="L220" s="65"/>
-      <c r="M220" s="67"/>
-      <c r="N220" s="66"/>
+      <c r="M220" s="66"/>
+      <c r="N220" s="69"/>
       <c r="O220" s="65" t="s">
         <v>48</v>
       </c>
@@ -10257,21 +10260,21 @@
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A221" s="68"/>
-      <c r="B221" s="67"/>
-      <c r="C221" s="67"/>
-      <c r="D221" s="67"/>
-      <c r="E221" s="67"/>
+      <c r="B221" s="66"/>
+      <c r="C221" s="66"/>
+      <c r="D221" s="66"/>
+      <c r="E221" s="66"/>
       <c r="F221" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="G221" s="69"/>
-      <c r="H221" s="70"/>
+      <c r="G221" s="70"/>
+      <c r="H221" s="73"/>
       <c r="I221" s="65"/>
-      <c r="J221" s="66"/>
-      <c r="K221" s="66"/>
+      <c r="J221" s="69"/>
+      <c r="K221" s="69"/>
       <c r="L221" s="65"/>
-      <c r="M221" s="67"/>
-      <c r="N221" s="66"/>
+      <c r="M221" s="66"/>
+      <c r="N221" s="69"/>
       <c r="O221" s="65"/>
       <c r="P221" s="65"/>
       <c r="Q221" s="65"/>
@@ -10319,35 +10322,35 @@
       <c r="A223" s="68">
         <v>140</v>
       </c>
-      <c r="B223" s="67" t="s">
+      <c r="B223" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="C223" s="67" t="s">
+      <c r="C223" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D223" s="67" t="s">
+      <c r="D223" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E223" s="67" t="s">
+      <c r="E223" s="66" t="s">
         <v>57</v>
       </c>
       <c r="F223" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="G223" s="69">
+      <c r="G223" s="70">
         <v>46129</v>
       </c>
-      <c r="H223" s="70" t="s">
+      <c r="H223" s="73" t="s">
         <v>425</v>
       </c>
       <c r="I223" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="J223" s="66"/>
-      <c r="K223" s="66"/>
+      <c r="J223" s="69"/>
+      <c r="K223" s="69"/>
       <c r="L223" s="65"/>
-      <c r="M223" s="67"/>
-      <c r="N223" s="66"/>
+      <c r="M223" s="66"/>
+      <c r="N223" s="69"/>
       <c r="O223" s="65" t="s">
         <v>63</v>
       </c>
@@ -10356,21 +10359,21 @@
     </row>
     <row r="224" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A224" s="68"/>
-      <c r="B224" s="67"/>
-      <c r="C224" s="67"/>
-      <c r="D224" s="67"/>
-      <c r="E224" s="67"/>
+      <c r="B224" s="66"/>
+      <c r="C224" s="66"/>
+      <c r="D224" s="66"/>
+      <c r="E224" s="66"/>
       <c r="F224" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="G224" s="69"/>
-      <c r="H224" s="70"/>
+      <c r="G224" s="70"/>
+      <c r="H224" s="73"/>
       <c r="I224" s="65"/>
-      <c r="J224" s="66"/>
-      <c r="K224" s="66"/>
+      <c r="J224" s="69"/>
+      <c r="K224" s="69"/>
       <c r="L224" s="65"/>
-      <c r="M224" s="67"/>
-      <c r="N224" s="66"/>
+      <c r="M224" s="66"/>
+      <c r="N224" s="69"/>
       <c r="O224" s="65"/>
       <c r="P224" s="65"/>
       <c r="Q224" s="65"/>
@@ -10570,31 +10573,31 @@
       <c r="A230" s="68">
         <v>146</v>
       </c>
-      <c r="B230" s="67" t="s">
+      <c r="B230" s="66" t="s">
         <v>442</v>
       </c>
-      <c r="C230" s="67" t="s">
+      <c r="C230" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D230" s="67"/>
-      <c r="E230" s="67" t="s">
+      <c r="D230" s="66"/>
+      <c r="E230" s="66" t="s">
         <v>57</v>
       </c>
       <c r="F230" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="G230" s="69">
+      <c r="G230" s="70">
         <v>46130</v>
       </c>
-      <c r="H230" s="70" t="s">
+      <c r="H230" s="73" t="s">
         <v>42</v>
       </c>
       <c r="I230" s="65"/>
-      <c r="J230" s="66"/>
-      <c r="K230" s="66"/>
+      <c r="J230" s="69"/>
+      <c r="K230" s="69"/>
       <c r="L230" s="65"/>
-      <c r="M230" s="67"/>
-      <c r="N230" s="66"/>
+      <c r="M230" s="66"/>
+      <c r="N230" s="69"/>
       <c r="O230" s="65" t="s">
         <v>447</v>
       </c>
@@ -10603,80 +10606,80 @@
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A231" s="68"/>
-      <c r="B231" s="67"/>
-      <c r="C231" s="67"/>
-      <c r="D231" s="67"/>
-      <c r="E231" s="67"/>
+      <c r="B231" s="66"/>
+      <c r="C231" s="66"/>
+      <c r="D231" s="66"/>
+      <c r="E231" s="66"/>
       <c r="F231" s="10"/>
-      <c r="G231" s="69"/>
-      <c r="H231" s="70"/>
+      <c r="G231" s="70"/>
+      <c r="H231" s="73"/>
       <c r="I231" s="65"/>
-      <c r="J231" s="66"/>
-      <c r="K231" s="66"/>
+      <c r="J231" s="69"/>
+      <c r="K231" s="69"/>
       <c r="L231" s="65"/>
-      <c r="M231" s="67"/>
-      <c r="N231" s="66"/>
+      <c r="M231" s="66"/>
+      <c r="N231" s="69"/>
       <c r="O231" s="65"/>
       <c r="P231" s="65"/>
       <c r="Q231" s="65"/>
     </row>
     <row r="232" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A232" s="68"/>
-      <c r="B232" s="67"/>
-      <c r="C232" s="67"/>
-      <c r="D232" s="67"/>
-      <c r="E232" s="67"/>
+      <c r="B232" s="66"/>
+      <c r="C232" s="66"/>
+      <c r="D232" s="66"/>
+      <c r="E232" s="66"/>
       <c r="F232" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="G232" s="69"/>
-      <c r="H232" s="70"/>
+      <c r="G232" s="70"/>
+      <c r="H232" s="73"/>
       <c r="I232" s="65"/>
-      <c r="J232" s="66"/>
-      <c r="K232" s="66"/>
+      <c r="J232" s="69"/>
+      <c r="K232" s="69"/>
       <c r="L232" s="65"/>
-      <c r="M232" s="67"/>
-      <c r="N232" s="66"/>
+      <c r="M232" s="66"/>
+      <c r="N232" s="69"/>
       <c r="O232" s="65"/>
       <c r="P232" s="65"/>
       <c r="Q232" s="65"/>
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A233" s="68"/>
-      <c r="B233" s="67"/>
-      <c r="C233" s="67"/>
-      <c r="D233" s="67"/>
-      <c r="E233" s="67"/>
+      <c r="B233" s="66"/>
+      <c r="C233" s="66"/>
+      <c r="D233" s="66"/>
+      <c r="E233" s="66"/>
       <c r="F233" s="11"/>
-      <c r="G233" s="69"/>
-      <c r="H233" s="70"/>
+      <c r="G233" s="70"/>
+      <c r="H233" s="73"/>
       <c r="I233" s="65"/>
-      <c r="J233" s="66"/>
-      <c r="K233" s="66"/>
+      <c r="J233" s="69"/>
+      <c r="K233" s="69"/>
       <c r="L233" s="65"/>
-      <c r="M233" s="67"/>
-      <c r="N233" s="66"/>
+      <c r="M233" s="66"/>
+      <c r="N233" s="69"/>
       <c r="O233" s="65"/>
       <c r="P233" s="65"/>
       <c r="Q233" s="65"/>
     </row>
     <row r="234" spans="1:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A234" s="68"/>
-      <c r="B234" s="67"/>
-      <c r="C234" s="67"/>
-      <c r="D234" s="67"/>
-      <c r="E234" s="67"/>
+      <c r="B234" s="66"/>
+      <c r="C234" s="66"/>
+      <c r="D234" s="66"/>
+      <c r="E234" s="66"/>
       <c r="F234" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="G234" s="69"/>
-      <c r="H234" s="70"/>
+      <c r="G234" s="70"/>
+      <c r="H234" s="73"/>
       <c r="I234" s="65"/>
-      <c r="J234" s="66"/>
-      <c r="K234" s="66"/>
+      <c r="J234" s="69"/>
+      <c r="K234" s="69"/>
       <c r="L234" s="65"/>
-      <c r="M234" s="67"/>
-      <c r="N234" s="66"/>
+      <c r="M234" s="66"/>
+      <c r="N234" s="69"/>
       <c r="O234" s="65"/>
       <c r="P234" s="65"/>
       <c r="Q234" s="65"/>
@@ -10685,33 +10688,33 @@
       <c r="A235" s="68">
         <v>147</v>
       </c>
-      <c r="B235" s="67" t="s">
+      <c r="B235" s="66" t="s">
         <v>442</v>
       </c>
-      <c r="C235" s="67" t="s">
+      <c r="C235" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D235" s="67" t="s">
+      <c r="D235" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E235" s="67" t="s">
+      <c r="E235" s="66" t="s">
         <v>20</v>
       </c>
       <c r="F235" s="24" t="s">
         <v>448</v>
       </c>
-      <c r="G235" s="69">
+      <c r="G235" s="70">
         <v>46130</v>
       </c>
-      <c r="H235" s="70" t="s">
+      <c r="H235" s="73" t="s">
         <v>42</v>
       </c>
       <c r="I235" s="65"/>
-      <c r="J235" s="66"/>
-      <c r="K235" s="66"/>
+      <c r="J235" s="69"/>
+      <c r="K235" s="69"/>
       <c r="L235" s="65"/>
-      <c r="M235" s="67"/>
-      <c r="N235" s="66"/>
+      <c r="M235" s="66"/>
+      <c r="N235" s="69"/>
       <c r="O235" s="65" t="s">
         <v>73</v>
       </c>
@@ -10720,21 +10723,21 @@
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A236" s="68"/>
-      <c r="B236" s="67"/>
-      <c r="C236" s="67"/>
-      <c r="D236" s="67"/>
-      <c r="E236" s="67"/>
+      <c r="B236" s="66"/>
+      <c r="C236" s="66"/>
+      <c r="D236" s="66"/>
+      <c r="E236" s="66"/>
       <c r="F236" s="24" t="s">
         <v>449</v>
       </c>
-      <c r="G236" s="69"/>
-      <c r="H236" s="70"/>
+      <c r="G236" s="70"/>
+      <c r="H236" s="73"/>
       <c r="I236" s="65"/>
-      <c r="J236" s="66"/>
-      <c r="K236" s="66"/>
+      <c r="J236" s="69"/>
+      <c r="K236" s="69"/>
       <c r="L236" s="65"/>
-      <c r="M236" s="67"/>
-      <c r="N236" s="66"/>
+      <c r="M236" s="66"/>
+      <c r="N236" s="69"/>
       <c r="O236" s="65"/>
       <c r="P236" s="65"/>
       <c r="Q236" s="65"/>
@@ -10742,6 +10745,680 @@
   </sheetData>
   <autoFilter ref="A1:Q236" xr:uid="{A1D28BEA-4422-41D8-B599-AD7035F3472A}"/>
   <mergeCells count="698">
+    <mergeCell ref="P235:P236"/>
+    <mergeCell ref="Q235:Q236"/>
+    <mergeCell ref="J235:J236"/>
+    <mergeCell ref="K235:K236"/>
+    <mergeCell ref="L235:L236"/>
+    <mergeCell ref="M235:M236"/>
+    <mergeCell ref="N235:N236"/>
+    <mergeCell ref="O235:O236"/>
+    <mergeCell ref="P230:P234"/>
+    <mergeCell ref="Q230:Q234"/>
+    <mergeCell ref="K230:K234"/>
+    <mergeCell ref="L230:L234"/>
+    <mergeCell ref="M230:M234"/>
+    <mergeCell ref="N230:N234"/>
+    <mergeCell ref="O230:O234"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="B235:B236"/>
+    <mergeCell ref="C235:C236"/>
+    <mergeCell ref="D235:D236"/>
+    <mergeCell ref="E235:E236"/>
+    <mergeCell ref="G235:G236"/>
+    <mergeCell ref="H235:H236"/>
+    <mergeCell ref="I235:I236"/>
+    <mergeCell ref="J230:J234"/>
+    <mergeCell ref="A230:A234"/>
+    <mergeCell ref="B230:B234"/>
+    <mergeCell ref="C230:C234"/>
+    <mergeCell ref="D230:D234"/>
+    <mergeCell ref="E230:E234"/>
+    <mergeCell ref="G230:G234"/>
+    <mergeCell ref="H230:H234"/>
+    <mergeCell ref="I230:I234"/>
+    <mergeCell ref="J223:J224"/>
+    <mergeCell ref="P220:P221"/>
+    <mergeCell ref="Q220:Q221"/>
+    <mergeCell ref="A223:A224"/>
+    <mergeCell ref="B223:B224"/>
+    <mergeCell ref="C223:C224"/>
+    <mergeCell ref="D223:D224"/>
+    <mergeCell ref="E223:E224"/>
+    <mergeCell ref="G223:G224"/>
+    <mergeCell ref="H223:H224"/>
+    <mergeCell ref="I223:I224"/>
+    <mergeCell ref="J220:J221"/>
+    <mergeCell ref="K220:K221"/>
+    <mergeCell ref="L220:L221"/>
+    <mergeCell ref="M220:M221"/>
+    <mergeCell ref="N220:N221"/>
+    <mergeCell ref="O220:O221"/>
+    <mergeCell ref="P223:P224"/>
+    <mergeCell ref="Q223:Q224"/>
+    <mergeCell ref="K223:K224"/>
+    <mergeCell ref="L223:L224"/>
+    <mergeCell ref="M223:M224"/>
+    <mergeCell ref="N223:N224"/>
+    <mergeCell ref="O223:O224"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="C220:C221"/>
+    <mergeCell ref="D220:D221"/>
+    <mergeCell ref="E220:E221"/>
+    <mergeCell ref="G220:G221"/>
+    <mergeCell ref="H220:H221"/>
+    <mergeCell ref="I220:I221"/>
+    <mergeCell ref="J212:J214"/>
+    <mergeCell ref="P205:P206"/>
+    <mergeCell ref="Q205:Q206"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="B212:B214"/>
+    <mergeCell ref="C212:C214"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="E212:E214"/>
+    <mergeCell ref="G212:G214"/>
+    <mergeCell ref="H212:H214"/>
+    <mergeCell ref="I212:I214"/>
+    <mergeCell ref="J205:J206"/>
+    <mergeCell ref="K205:K206"/>
+    <mergeCell ref="L205:L206"/>
+    <mergeCell ref="M205:M206"/>
+    <mergeCell ref="N205:N206"/>
+    <mergeCell ref="O205:O206"/>
+    <mergeCell ref="P212:P214"/>
+    <mergeCell ref="Q212:Q214"/>
+    <mergeCell ref="K212:K214"/>
+    <mergeCell ref="L212:L214"/>
+    <mergeCell ref="M212:M214"/>
+    <mergeCell ref="N212:N214"/>
+    <mergeCell ref="O212:O214"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="B205:B206"/>
+    <mergeCell ref="C205:C206"/>
+    <mergeCell ref="D205:D206"/>
+    <mergeCell ref="E205:E206"/>
+    <mergeCell ref="G205:G206"/>
+    <mergeCell ref="H205:H206"/>
+    <mergeCell ref="I205:I206"/>
+    <mergeCell ref="J203:J204"/>
+    <mergeCell ref="P201:P202"/>
+    <mergeCell ref="Q201:Q202"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="B203:B204"/>
+    <mergeCell ref="C203:C204"/>
+    <mergeCell ref="D203:D204"/>
+    <mergeCell ref="E203:E204"/>
+    <mergeCell ref="G203:G204"/>
+    <mergeCell ref="H203:H204"/>
+    <mergeCell ref="I203:I204"/>
+    <mergeCell ref="J201:J202"/>
+    <mergeCell ref="K201:K202"/>
+    <mergeCell ref="L201:L202"/>
+    <mergeCell ref="M201:M202"/>
+    <mergeCell ref="N201:N202"/>
+    <mergeCell ref="O201:O202"/>
+    <mergeCell ref="P203:P204"/>
+    <mergeCell ref="Q203:Q204"/>
+    <mergeCell ref="K203:K204"/>
+    <mergeCell ref="L203:L204"/>
+    <mergeCell ref="M203:M204"/>
+    <mergeCell ref="N203:N204"/>
+    <mergeCell ref="O203:O204"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="C201:C202"/>
+    <mergeCell ref="D201:D202"/>
+    <mergeCell ref="E201:E202"/>
+    <mergeCell ref="G201:G202"/>
+    <mergeCell ref="H201:H202"/>
+    <mergeCell ref="I201:I202"/>
+    <mergeCell ref="J199:J200"/>
+    <mergeCell ref="P189:P192"/>
+    <mergeCell ref="Q189:Q192"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="B199:B200"/>
+    <mergeCell ref="C199:C200"/>
+    <mergeCell ref="D199:D200"/>
+    <mergeCell ref="E199:E200"/>
+    <mergeCell ref="G199:G200"/>
+    <mergeCell ref="H199:H200"/>
+    <mergeCell ref="I199:I200"/>
+    <mergeCell ref="J189:J192"/>
+    <mergeCell ref="K189:K192"/>
+    <mergeCell ref="L189:L192"/>
+    <mergeCell ref="M189:M192"/>
+    <mergeCell ref="N189:N192"/>
+    <mergeCell ref="O189:O192"/>
+    <mergeCell ref="P199:P200"/>
+    <mergeCell ref="Q199:Q200"/>
+    <mergeCell ref="K199:K200"/>
+    <mergeCell ref="L199:L200"/>
+    <mergeCell ref="M199:M200"/>
+    <mergeCell ref="N199:N200"/>
+    <mergeCell ref="O199:O200"/>
+    <mergeCell ref="A189:A192"/>
+    <mergeCell ref="B189:B192"/>
+    <mergeCell ref="C189:C192"/>
+    <mergeCell ref="D189:D192"/>
+    <mergeCell ref="E189:E192"/>
+    <mergeCell ref="G189:G192"/>
+    <mergeCell ref="H189:H192"/>
+    <mergeCell ref="I189:I192"/>
+    <mergeCell ref="J178:J179"/>
+    <mergeCell ref="P169:P170"/>
+    <mergeCell ref="Q169:Q170"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="D178:D179"/>
+    <mergeCell ref="E178:E179"/>
+    <mergeCell ref="G178:G179"/>
+    <mergeCell ref="H178:H179"/>
+    <mergeCell ref="I178:I179"/>
+    <mergeCell ref="J169:J170"/>
+    <mergeCell ref="K169:K170"/>
+    <mergeCell ref="L169:L170"/>
+    <mergeCell ref="M169:M170"/>
+    <mergeCell ref="N169:N170"/>
+    <mergeCell ref="O169:O170"/>
+    <mergeCell ref="P178:P179"/>
+    <mergeCell ref="Q178:Q179"/>
+    <mergeCell ref="K178:K179"/>
+    <mergeCell ref="L178:L179"/>
+    <mergeCell ref="M178:M179"/>
+    <mergeCell ref="N178:N179"/>
+    <mergeCell ref="O178:O179"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="C169:C170"/>
+    <mergeCell ref="D169:D170"/>
+    <mergeCell ref="E169:E170"/>
+    <mergeCell ref="G169:G170"/>
+    <mergeCell ref="H169:H170"/>
+    <mergeCell ref="I169:I170"/>
+    <mergeCell ref="J149:J168"/>
+    <mergeCell ref="P144:P148"/>
+    <mergeCell ref="Q144:Q148"/>
+    <mergeCell ref="A149:A168"/>
+    <mergeCell ref="B149:B168"/>
+    <mergeCell ref="C149:C168"/>
+    <mergeCell ref="D149:D168"/>
+    <mergeCell ref="E149:E168"/>
+    <mergeCell ref="G149:G168"/>
+    <mergeCell ref="H149:H168"/>
+    <mergeCell ref="I149:I168"/>
+    <mergeCell ref="I144:I148"/>
+    <mergeCell ref="J144:J148"/>
+    <mergeCell ref="K144:K148"/>
+    <mergeCell ref="L144:L148"/>
+    <mergeCell ref="N144:N148"/>
+    <mergeCell ref="O144:O148"/>
+    <mergeCell ref="P149:P168"/>
+    <mergeCell ref="Q149:Q168"/>
+    <mergeCell ref="K149:K168"/>
+    <mergeCell ref="L149:L168"/>
+    <mergeCell ref="M149:M168"/>
+    <mergeCell ref="N149:N168"/>
+    <mergeCell ref="O149:O168"/>
+    <mergeCell ref="A144:A148"/>
+    <mergeCell ref="B144:B148"/>
+    <mergeCell ref="C144:C148"/>
+    <mergeCell ref="D144:D148"/>
+    <mergeCell ref="E144:E148"/>
+    <mergeCell ref="G144:G148"/>
+    <mergeCell ref="H144:H148"/>
+    <mergeCell ref="I141:I142"/>
+    <mergeCell ref="J141:J142"/>
+    <mergeCell ref="O139:O140"/>
+    <mergeCell ref="P139:P140"/>
+    <mergeCell ref="Q139:Q140"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="D141:D142"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="G141:G142"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="J139:J140"/>
+    <mergeCell ref="K139:K140"/>
+    <mergeCell ref="L139:L140"/>
+    <mergeCell ref="M139:M140"/>
+    <mergeCell ref="N139:N140"/>
+    <mergeCell ref="O141:O142"/>
+    <mergeCell ref="P141:P142"/>
+    <mergeCell ref="Q141:Q142"/>
+    <mergeCell ref="K141:K142"/>
+    <mergeCell ref="L141:L142"/>
+    <mergeCell ref="M141:M142"/>
+    <mergeCell ref="N141:N142"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="E139:E140"/>
+    <mergeCell ref="G139:G140"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="H136:H138"/>
+    <mergeCell ref="I136:I138"/>
+    <mergeCell ref="N134:N135"/>
+    <mergeCell ref="O134:O135"/>
+    <mergeCell ref="P134:P135"/>
+    <mergeCell ref="Q134:Q135"/>
+    <mergeCell ref="A136:A138"/>
+    <mergeCell ref="B136:B138"/>
+    <mergeCell ref="C136:C138"/>
+    <mergeCell ref="D136:D138"/>
+    <mergeCell ref="E136:E138"/>
+    <mergeCell ref="G136:G138"/>
+    <mergeCell ref="H134:H135"/>
+    <mergeCell ref="I134:I135"/>
+    <mergeCell ref="J134:J135"/>
+    <mergeCell ref="K134:K135"/>
+    <mergeCell ref="L134:L135"/>
+    <mergeCell ref="M134:M135"/>
+    <mergeCell ref="O136:O138"/>
+    <mergeCell ref="P136:P138"/>
+    <mergeCell ref="Q136:Q138"/>
+    <mergeCell ref="J136:J138"/>
+    <mergeCell ref="K136:K138"/>
+    <mergeCell ref="L136:L138"/>
+    <mergeCell ref="N136:N138"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
+    <mergeCell ref="E134:E135"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="H132:H133"/>
+    <mergeCell ref="I132:I133"/>
+    <mergeCell ref="J132:J133"/>
+    <mergeCell ref="P130:P131"/>
+    <mergeCell ref="Q130:Q131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="E132:E133"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="H130:H131"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="K130:K131"/>
+    <mergeCell ref="L130:L131"/>
+    <mergeCell ref="M130:M131"/>
+    <mergeCell ref="N132:N133"/>
+    <mergeCell ref="O132:O133"/>
+    <mergeCell ref="P132:P133"/>
+    <mergeCell ref="Q132:Q133"/>
+    <mergeCell ref="K132:K133"/>
+    <mergeCell ref="L132:L133"/>
+    <mergeCell ref="M132:M133"/>
+    <mergeCell ref="N127:N129"/>
+    <mergeCell ref="O127:O129"/>
+    <mergeCell ref="P127:P129"/>
+    <mergeCell ref="Q127:Q129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="G130:G131"/>
+    <mergeCell ref="H127:H129"/>
+    <mergeCell ref="I127:I129"/>
+    <mergeCell ref="J127:J129"/>
+    <mergeCell ref="K127:K129"/>
+    <mergeCell ref="L127:L129"/>
+    <mergeCell ref="M127:M129"/>
+    <mergeCell ref="A127:A129"/>
+    <mergeCell ref="B127:B129"/>
+    <mergeCell ref="C127:C129"/>
+    <mergeCell ref="D127:D129"/>
+    <mergeCell ref="E127:E129"/>
+    <mergeCell ref="G127:G129"/>
+    <mergeCell ref="N130:N131"/>
+    <mergeCell ref="O130:O131"/>
+    <mergeCell ref="K125:K126"/>
+    <mergeCell ref="L125:L126"/>
+    <mergeCell ref="N125:N126"/>
+    <mergeCell ref="O125:O126"/>
+    <mergeCell ref="P125:P126"/>
+    <mergeCell ref="Q125:Q126"/>
+    <mergeCell ref="Q123:Q124"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="D125:D126"/>
+    <mergeCell ref="E125:E126"/>
+    <mergeCell ref="G125:G126"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="J125:J126"/>
+    <mergeCell ref="J123:J124"/>
+    <mergeCell ref="K123:K124"/>
+    <mergeCell ref="L123:L124"/>
+    <mergeCell ref="N123:N124"/>
+    <mergeCell ref="O123:O124"/>
+    <mergeCell ref="P123:P124"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="D123:D124"/>
+    <mergeCell ref="E123:E124"/>
+    <mergeCell ref="G123:G124"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="J118:J119"/>
+    <mergeCell ref="P112:P113"/>
+    <mergeCell ref="Q112:Q113"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="E118:E119"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="H118:H119"/>
+    <mergeCell ref="I118:I119"/>
+    <mergeCell ref="J112:J113"/>
+    <mergeCell ref="K112:K113"/>
+    <mergeCell ref="L112:L113"/>
+    <mergeCell ref="M112:M113"/>
+    <mergeCell ref="N112:N113"/>
+    <mergeCell ref="O112:O113"/>
+    <mergeCell ref="P118:P119"/>
+    <mergeCell ref="Q118:Q119"/>
+    <mergeCell ref="K118:K119"/>
+    <mergeCell ref="L118:L119"/>
+    <mergeCell ref="M118:M119"/>
+    <mergeCell ref="N118:N119"/>
+    <mergeCell ref="O118:O119"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="E112:E113"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="H112:H113"/>
+    <mergeCell ref="I112:I113"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="P95:P99"/>
+    <mergeCell ref="Q95:Q99"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="H104:H105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J95:J99"/>
+    <mergeCell ref="K95:K99"/>
+    <mergeCell ref="L95:L99"/>
+    <mergeCell ref="M95:M99"/>
+    <mergeCell ref="N95:N99"/>
+    <mergeCell ref="O95:O99"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="Q104:Q105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="A95:A99"/>
+    <mergeCell ref="B95:B99"/>
+    <mergeCell ref="C95:C99"/>
+    <mergeCell ref="D95:D99"/>
+    <mergeCell ref="E95:E99"/>
+    <mergeCell ref="G95:G99"/>
+    <mergeCell ref="H95:H99"/>
+    <mergeCell ref="I95:I99"/>
+    <mergeCell ref="J92:J93"/>
+    <mergeCell ref="P89:P90"/>
+    <mergeCell ref="Q89:Q90"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="H92:H93"/>
+    <mergeCell ref="I92:I93"/>
+    <mergeCell ref="J89:J90"/>
+    <mergeCell ref="K89:K90"/>
+    <mergeCell ref="L89:L90"/>
+    <mergeCell ref="M89:M90"/>
+    <mergeCell ref="N89:N90"/>
+    <mergeCell ref="O89:O90"/>
+    <mergeCell ref="P92:P93"/>
+    <mergeCell ref="Q92:Q93"/>
+    <mergeCell ref="K92:K93"/>
+    <mergeCell ref="L92:L93"/>
+    <mergeCell ref="M92:M93"/>
+    <mergeCell ref="N92:N93"/>
+    <mergeCell ref="O92:O93"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="D89:D90"/>
+    <mergeCell ref="E89:E90"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="J79:J85"/>
+    <mergeCell ref="P69:P70"/>
+    <mergeCell ref="Q69:Q70"/>
+    <mergeCell ref="A79:A85"/>
+    <mergeCell ref="B79:B85"/>
+    <mergeCell ref="C79:C85"/>
+    <mergeCell ref="D79:D85"/>
+    <mergeCell ref="E79:E85"/>
+    <mergeCell ref="G79:G85"/>
+    <mergeCell ref="H79:H85"/>
+    <mergeCell ref="I79:I85"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="N69:N70"/>
+    <mergeCell ref="O69:O70"/>
+    <mergeCell ref="P79:P85"/>
+    <mergeCell ref="Q79:Q85"/>
+    <mergeCell ref="K79:K85"/>
+    <mergeCell ref="L79:L85"/>
+    <mergeCell ref="M79:M85"/>
+    <mergeCell ref="N79:N85"/>
+    <mergeCell ref="O79:O85"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="J67:J68"/>
+    <mergeCell ref="P61:P65"/>
+    <mergeCell ref="Q61:Q65"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="J61:J65"/>
+    <mergeCell ref="K61:K65"/>
+    <mergeCell ref="L61:L65"/>
+    <mergeCell ref="M61:M65"/>
+    <mergeCell ref="N61:N65"/>
+    <mergeCell ref="O61:O65"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="Q67:Q68"/>
+    <mergeCell ref="K67:K68"/>
+    <mergeCell ref="L67:L68"/>
+    <mergeCell ref="M67:M68"/>
+    <mergeCell ref="N67:N68"/>
+    <mergeCell ref="O67:O68"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
+    <mergeCell ref="E61:E65"/>
+    <mergeCell ref="G61:G65"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="I61:I65"/>
+    <mergeCell ref="J58:J60"/>
+    <mergeCell ref="P56:P57"/>
+    <mergeCell ref="Q56:Q57"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="G58:G60"/>
+    <mergeCell ref="H58:H60"/>
+    <mergeCell ref="I58:I60"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="L56:L57"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="N56:N57"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="P58:P60"/>
+    <mergeCell ref="Q58:Q60"/>
+    <mergeCell ref="K58:K60"/>
+    <mergeCell ref="L58:L60"/>
+    <mergeCell ref="M58:M60"/>
+    <mergeCell ref="N58:N60"/>
+    <mergeCell ref="O58:O60"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="P51:P53"/>
+    <mergeCell ref="Q51:Q53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="I51:I53"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="K51:K53"/>
+    <mergeCell ref="L51:L53"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="O51:O53"/>
+    <mergeCell ref="P54:P55"/>
+    <mergeCell ref="Q54:Q55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="M54:M55"/>
+    <mergeCell ref="N54:N55"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="N44:N45"/>
+    <mergeCell ref="O44:O45"/>
+    <mergeCell ref="P44:P45"/>
+    <mergeCell ref="Q44:Q45"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N38:N39"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="P38:P39"/>
+    <mergeCell ref="Q38:Q39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="O18:O20"/>
+    <mergeCell ref="P18:P20"/>
+    <mergeCell ref="Q18:Q20"/>
+    <mergeCell ref="K18:K20"/>
+    <mergeCell ref="L18:L20"/>
+    <mergeCell ref="M18:M20"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -10766,680 +11443,6 @@
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="N15:N17"/>
     <mergeCell ref="O15:O17"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="K15:K17"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="O18:O20"/>
-    <mergeCell ref="P18:P20"/>
-    <mergeCell ref="Q18:Q20"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="I18:I20"/>
-    <mergeCell ref="J18:J20"/>
-    <mergeCell ref="K18:K20"/>
-    <mergeCell ref="L18:L20"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N38:N39"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="P38:P39"/>
-    <mergeCell ref="Q38:Q39"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="N44:N45"/>
-    <mergeCell ref="O44:O45"/>
-    <mergeCell ref="P44:P45"/>
-    <mergeCell ref="Q44:Q45"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="F51:F53"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="P51:P53"/>
-    <mergeCell ref="Q51:Q53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="I51:I53"/>
-    <mergeCell ref="J51:J53"/>
-    <mergeCell ref="K51:K53"/>
-    <mergeCell ref="L51:L53"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="O51:O53"/>
-    <mergeCell ref="P54:P55"/>
-    <mergeCell ref="Q54:Q55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="L54:L55"/>
-    <mergeCell ref="M54:M55"/>
-    <mergeCell ref="N54:N55"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="P56:P57"/>
-    <mergeCell ref="Q56:Q57"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="D58:D60"/>
-    <mergeCell ref="E58:E60"/>
-    <mergeCell ref="G58:G60"/>
-    <mergeCell ref="H58:H60"/>
-    <mergeCell ref="I58:I60"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="L56:L57"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="N56:N57"/>
-    <mergeCell ref="O56:O57"/>
-    <mergeCell ref="P58:P60"/>
-    <mergeCell ref="Q58:Q60"/>
-    <mergeCell ref="A61:A65"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:C65"/>
-    <mergeCell ref="D61:D65"/>
-    <mergeCell ref="E61:E65"/>
-    <mergeCell ref="G61:G65"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="I61:I65"/>
-    <mergeCell ref="J58:J60"/>
-    <mergeCell ref="K58:K60"/>
-    <mergeCell ref="L58:L60"/>
-    <mergeCell ref="M58:M60"/>
-    <mergeCell ref="N58:N60"/>
-    <mergeCell ref="O58:O60"/>
-    <mergeCell ref="P61:P65"/>
-    <mergeCell ref="Q61:Q65"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="J61:J65"/>
-    <mergeCell ref="K61:K65"/>
-    <mergeCell ref="L61:L65"/>
-    <mergeCell ref="M61:M65"/>
-    <mergeCell ref="N61:N65"/>
-    <mergeCell ref="O61:O65"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="Q67:Q68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="J67:J68"/>
-    <mergeCell ref="K67:K68"/>
-    <mergeCell ref="L67:L68"/>
-    <mergeCell ref="M67:M68"/>
-    <mergeCell ref="N67:N68"/>
-    <mergeCell ref="O67:O68"/>
-    <mergeCell ref="P69:P70"/>
-    <mergeCell ref="Q69:Q70"/>
-    <mergeCell ref="A79:A85"/>
-    <mergeCell ref="B79:B85"/>
-    <mergeCell ref="C79:C85"/>
-    <mergeCell ref="D79:D85"/>
-    <mergeCell ref="E79:E85"/>
-    <mergeCell ref="G79:G85"/>
-    <mergeCell ref="H79:H85"/>
-    <mergeCell ref="I79:I85"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="O69:O70"/>
-    <mergeCell ref="P79:P85"/>
-    <mergeCell ref="Q79:Q85"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="D89:D90"/>
-    <mergeCell ref="E89:E90"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="J79:J85"/>
-    <mergeCell ref="K79:K85"/>
-    <mergeCell ref="L79:L85"/>
-    <mergeCell ref="M79:M85"/>
-    <mergeCell ref="N79:N85"/>
-    <mergeCell ref="O79:O85"/>
-    <mergeCell ref="P89:P90"/>
-    <mergeCell ref="Q89:Q90"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="H92:H93"/>
-    <mergeCell ref="I92:I93"/>
-    <mergeCell ref="J89:J90"/>
-    <mergeCell ref="K89:K90"/>
-    <mergeCell ref="L89:L90"/>
-    <mergeCell ref="M89:M90"/>
-    <mergeCell ref="N89:N90"/>
-    <mergeCell ref="O89:O90"/>
-    <mergeCell ref="P92:P93"/>
-    <mergeCell ref="Q92:Q93"/>
-    <mergeCell ref="A95:A99"/>
-    <mergeCell ref="B95:B99"/>
-    <mergeCell ref="C95:C99"/>
-    <mergeCell ref="D95:D99"/>
-    <mergeCell ref="E95:E99"/>
-    <mergeCell ref="G95:G99"/>
-    <mergeCell ref="H95:H99"/>
-    <mergeCell ref="I95:I99"/>
-    <mergeCell ref="J92:J93"/>
-    <mergeCell ref="K92:K93"/>
-    <mergeCell ref="L92:L93"/>
-    <mergeCell ref="M92:M93"/>
-    <mergeCell ref="N92:N93"/>
-    <mergeCell ref="O92:O93"/>
-    <mergeCell ref="P95:P99"/>
-    <mergeCell ref="Q95:Q99"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="H104:H105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J95:J99"/>
-    <mergeCell ref="K95:K99"/>
-    <mergeCell ref="L95:L99"/>
-    <mergeCell ref="M95:M99"/>
-    <mergeCell ref="N95:N99"/>
-    <mergeCell ref="O95:O99"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="Q104:Q105"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="D112:D113"/>
-    <mergeCell ref="E112:E113"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="H112:H113"/>
-    <mergeCell ref="I112:I113"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P112:P113"/>
-    <mergeCell ref="Q112:Q113"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="E118:E119"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="H118:H119"/>
-    <mergeCell ref="I118:I119"/>
-    <mergeCell ref="J112:J113"/>
-    <mergeCell ref="K112:K113"/>
-    <mergeCell ref="L112:L113"/>
-    <mergeCell ref="M112:M113"/>
-    <mergeCell ref="N112:N113"/>
-    <mergeCell ref="O112:O113"/>
-    <mergeCell ref="P118:P119"/>
-    <mergeCell ref="Q118:Q119"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="D123:D124"/>
-    <mergeCell ref="E123:E124"/>
-    <mergeCell ref="G123:G124"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="J118:J119"/>
-    <mergeCell ref="K118:K119"/>
-    <mergeCell ref="L118:L119"/>
-    <mergeCell ref="M118:M119"/>
-    <mergeCell ref="N118:N119"/>
-    <mergeCell ref="O118:O119"/>
-    <mergeCell ref="K125:K126"/>
-    <mergeCell ref="L125:L126"/>
-    <mergeCell ref="N125:N126"/>
-    <mergeCell ref="O125:O126"/>
-    <mergeCell ref="P125:P126"/>
-    <mergeCell ref="Q125:Q126"/>
-    <mergeCell ref="Q123:Q124"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="C125:C126"/>
-    <mergeCell ref="D125:D126"/>
-    <mergeCell ref="E125:E126"/>
-    <mergeCell ref="G125:G126"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="J125:J126"/>
-    <mergeCell ref="J123:J124"/>
-    <mergeCell ref="K123:K124"/>
-    <mergeCell ref="L123:L124"/>
-    <mergeCell ref="N123:N124"/>
-    <mergeCell ref="O123:O124"/>
-    <mergeCell ref="P123:P124"/>
-    <mergeCell ref="N127:N129"/>
-    <mergeCell ref="O127:O129"/>
-    <mergeCell ref="P127:P129"/>
-    <mergeCell ref="Q127:Q129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="G130:G131"/>
-    <mergeCell ref="H127:H129"/>
-    <mergeCell ref="I127:I129"/>
-    <mergeCell ref="J127:J129"/>
-    <mergeCell ref="K127:K129"/>
-    <mergeCell ref="L127:L129"/>
-    <mergeCell ref="M127:M129"/>
-    <mergeCell ref="A127:A129"/>
-    <mergeCell ref="B127:B129"/>
-    <mergeCell ref="C127:C129"/>
-    <mergeCell ref="D127:D129"/>
-    <mergeCell ref="E127:E129"/>
-    <mergeCell ref="G127:G129"/>
-    <mergeCell ref="N130:N131"/>
-    <mergeCell ref="O130:O131"/>
-    <mergeCell ref="P130:P131"/>
-    <mergeCell ref="Q130:Q131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D132:D133"/>
-    <mergeCell ref="E132:E133"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="K130:K131"/>
-    <mergeCell ref="L130:L131"/>
-    <mergeCell ref="M130:M131"/>
-    <mergeCell ref="N132:N133"/>
-    <mergeCell ref="O132:O133"/>
-    <mergeCell ref="P132:P133"/>
-    <mergeCell ref="Q132:Q133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:D135"/>
-    <mergeCell ref="E134:E135"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="H132:H133"/>
-    <mergeCell ref="I132:I133"/>
-    <mergeCell ref="J132:J133"/>
-    <mergeCell ref="K132:K133"/>
-    <mergeCell ref="L132:L133"/>
-    <mergeCell ref="M132:M133"/>
-    <mergeCell ref="N134:N135"/>
-    <mergeCell ref="O134:O135"/>
-    <mergeCell ref="P134:P135"/>
-    <mergeCell ref="Q134:Q135"/>
-    <mergeCell ref="A136:A138"/>
-    <mergeCell ref="B136:B138"/>
-    <mergeCell ref="C136:C138"/>
-    <mergeCell ref="D136:D138"/>
-    <mergeCell ref="E136:E138"/>
-    <mergeCell ref="G136:G138"/>
-    <mergeCell ref="H134:H135"/>
-    <mergeCell ref="I134:I135"/>
-    <mergeCell ref="J134:J135"/>
-    <mergeCell ref="K134:K135"/>
-    <mergeCell ref="L134:L135"/>
-    <mergeCell ref="M134:M135"/>
-    <mergeCell ref="O136:O138"/>
-    <mergeCell ref="P136:P138"/>
-    <mergeCell ref="Q136:Q138"/>
-    <mergeCell ref="A139:A140"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="C139:C140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="E139:E140"/>
-    <mergeCell ref="G139:G140"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="H136:H138"/>
-    <mergeCell ref="I136:I138"/>
-    <mergeCell ref="J136:J138"/>
-    <mergeCell ref="K136:K138"/>
-    <mergeCell ref="L136:L138"/>
-    <mergeCell ref="N136:N138"/>
-    <mergeCell ref="O139:O140"/>
-    <mergeCell ref="P139:P140"/>
-    <mergeCell ref="Q139:Q140"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="D141:D142"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="G141:G142"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="K139:K140"/>
-    <mergeCell ref="L139:L140"/>
-    <mergeCell ref="M139:M140"/>
-    <mergeCell ref="N139:N140"/>
-    <mergeCell ref="O141:O142"/>
-    <mergeCell ref="P141:P142"/>
-    <mergeCell ref="Q141:Q142"/>
-    <mergeCell ref="A144:A148"/>
-    <mergeCell ref="B144:B148"/>
-    <mergeCell ref="C144:C148"/>
-    <mergeCell ref="D144:D148"/>
-    <mergeCell ref="E144:E148"/>
-    <mergeCell ref="G144:G148"/>
-    <mergeCell ref="H144:H148"/>
-    <mergeCell ref="I141:I142"/>
-    <mergeCell ref="J141:J142"/>
-    <mergeCell ref="K141:K142"/>
-    <mergeCell ref="L141:L142"/>
-    <mergeCell ref="M141:M142"/>
-    <mergeCell ref="N141:N142"/>
-    <mergeCell ref="P144:P148"/>
-    <mergeCell ref="Q144:Q148"/>
-    <mergeCell ref="A149:A168"/>
-    <mergeCell ref="B149:B168"/>
-    <mergeCell ref="C149:C168"/>
-    <mergeCell ref="D149:D168"/>
-    <mergeCell ref="E149:E168"/>
-    <mergeCell ref="G149:G168"/>
-    <mergeCell ref="H149:H168"/>
-    <mergeCell ref="I149:I168"/>
-    <mergeCell ref="I144:I148"/>
-    <mergeCell ref="J144:J148"/>
-    <mergeCell ref="K144:K148"/>
-    <mergeCell ref="L144:L148"/>
-    <mergeCell ref="N144:N148"/>
-    <mergeCell ref="O144:O148"/>
-    <mergeCell ref="P149:P168"/>
-    <mergeCell ref="Q149:Q168"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="C169:C170"/>
-    <mergeCell ref="D169:D170"/>
-    <mergeCell ref="E169:E170"/>
-    <mergeCell ref="G169:G170"/>
-    <mergeCell ref="H169:H170"/>
-    <mergeCell ref="I169:I170"/>
-    <mergeCell ref="J149:J168"/>
-    <mergeCell ref="K149:K168"/>
-    <mergeCell ref="L149:L168"/>
-    <mergeCell ref="M149:M168"/>
-    <mergeCell ref="N149:N168"/>
-    <mergeCell ref="O149:O168"/>
-    <mergeCell ref="P169:P170"/>
-    <mergeCell ref="Q169:Q170"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="D178:D179"/>
-    <mergeCell ref="E178:E179"/>
-    <mergeCell ref="G178:G179"/>
-    <mergeCell ref="H178:H179"/>
-    <mergeCell ref="I178:I179"/>
-    <mergeCell ref="J169:J170"/>
-    <mergeCell ref="K169:K170"/>
-    <mergeCell ref="L169:L170"/>
-    <mergeCell ref="M169:M170"/>
-    <mergeCell ref="N169:N170"/>
-    <mergeCell ref="O169:O170"/>
-    <mergeCell ref="P178:P179"/>
-    <mergeCell ref="Q178:Q179"/>
-    <mergeCell ref="A189:A192"/>
-    <mergeCell ref="B189:B192"/>
-    <mergeCell ref="C189:C192"/>
-    <mergeCell ref="D189:D192"/>
-    <mergeCell ref="E189:E192"/>
-    <mergeCell ref="G189:G192"/>
-    <mergeCell ref="H189:H192"/>
-    <mergeCell ref="I189:I192"/>
-    <mergeCell ref="J178:J179"/>
-    <mergeCell ref="K178:K179"/>
-    <mergeCell ref="L178:L179"/>
-    <mergeCell ref="M178:M179"/>
-    <mergeCell ref="N178:N179"/>
-    <mergeCell ref="O178:O179"/>
-    <mergeCell ref="P189:P192"/>
-    <mergeCell ref="Q189:Q192"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="B199:B200"/>
-    <mergeCell ref="C199:C200"/>
-    <mergeCell ref="D199:D200"/>
-    <mergeCell ref="E199:E200"/>
-    <mergeCell ref="G199:G200"/>
-    <mergeCell ref="H199:H200"/>
-    <mergeCell ref="I199:I200"/>
-    <mergeCell ref="J189:J192"/>
-    <mergeCell ref="K189:K192"/>
-    <mergeCell ref="L189:L192"/>
-    <mergeCell ref="M189:M192"/>
-    <mergeCell ref="N189:N192"/>
-    <mergeCell ref="O189:O192"/>
-    <mergeCell ref="P199:P200"/>
-    <mergeCell ref="Q199:Q200"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="B201:B202"/>
-    <mergeCell ref="C201:C202"/>
-    <mergeCell ref="D201:D202"/>
-    <mergeCell ref="E201:E202"/>
-    <mergeCell ref="G201:G202"/>
-    <mergeCell ref="H201:H202"/>
-    <mergeCell ref="I201:I202"/>
-    <mergeCell ref="J199:J200"/>
-    <mergeCell ref="K199:K200"/>
-    <mergeCell ref="L199:L200"/>
-    <mergeCell ref="M199:M200"/>
-    <mergeCell ref="N199:N200"/>
-    <mergeCell ref="O199:O200"/>
-    <mergeCell ref="P201:P202"/>
-    <mergeCell ref="Q201:Q202"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="B203:B204"/>
-    <mergeCell ref="C203:C204"/>
-    <mergeCell ref="D203:D204"/>
-    <mergeCell ref="E203:E204"/>
-    <mergeCell ref="G203:G204"/>
-    <mergeCell ref="H203:H204"/>
-    <mergeCell ref="I203:I204"/>
-    <mergeCell ref="J201:J202"/>
-    <mergeCell ref="K201:K202"/>
-    <mergeCell ref="L201:L202"/>
-    <mergeCell ref="M201:M202"/>
-    <mergeCell ref="N201:N202"/>
-    <mergeCell ref="O201:O202"/>
-    <mergeCell ref="P203:P204"/>
-    <mergeCell ref="Q203:Q204"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="B205:B206"/>
-    <mergeCell ref="C205:C206"/>
-    <mergeCell ref="D205:D206"/>
-    <mergeCell ref="E205:E206"/>
-    <mergeCell ref="G205:G206"/>
-    <mergeCell ref="H205:H206"/>
-    <mergeCell ref="I205:I206"/>
-    <mergeCell ref="J203:J204"/>
-    <mergeCell ref="K203:K204"/>
-    <mergeCell ref="L203:L204"/>
-    <mergeCell ref="M203:M204"/>
-    <mergeCell ref="N203:N204"/>
-    <mergeCell ref="O203:O204"/>
-    <mergeCell ref="P205:P206"/>
-    <mergeCell ref="Q205:Q206"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="B212:B214"/>
-    <mergeCell ref="C212:C214"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="E212:E214"/>
-    <mergeCell ref="G212:G214"/>
-    <mergeCell ref="H212:H214"/>
-    <mergeCell ref="I212:I214"/>
-    <mergeCell ref="J205:J206"/>
-    <mergeCell ref="K205:K206"/>
-    <mergeCell ref="L205:L206"/>
-    <mergeCell ref="M205:M206"/>
-    <mergeCell ref="N205:N206"/>
-    <mergeCell ref="O205:O206"/>
-    <mergeCell ref="P212:P214"/>
-    <mergeCell ref="Q212:Q214"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="C220:C221"/>
-    <mergeCell ref="D220:D221"/>
-    <mergeCell ref="E220:E221"/>
-    <mergeCell ref="G220:G221"/>
-    <mergeCell ref="H220:H221"/>
-    <mergeCell ref="I220:I221"/>
-    <mergeCell ref="J212:J214"/>
-    <mergeCell ref="K212:K214"/>
-    <mergeCell ref="L212:L214"/>
-    <mergeCell ref="M212:M214"/>
-    <mergeCell ref="N212:N214"/>
-    <mergeCell ref="O212:O214"/>
-    <mergeCell ref="P220:P221"/>
-    <mergeCell ref="Q220:Q221"/>
-    <mergeCell ref="A223:A224"/>
-    <mergeCell ref="B223:B224"/>
-    <mergeCell ref="C223:C224"/>
-    <mergeCell ref="D223:D224"/>
-    <mergeCell ref="E223:E224"/>
-    <mergeCell ref="G223:G224"/>
-    <mergeCell ref="H223:H224"/>
-    <mergeCell ref="I223:I224"/>
-    <mergeCell ref="J220:J221"/>
-    <mergeCell ref="K220:K221"/>
-    <mergeCell ref="L220:L221"/>
-    <mergeCell ref="M220:M221"/>
-    <mergeCell ref="N220:N221"/>
-    <mergeCell ref="O220:O221"/>
-    <mergeCell ref="P223:P224"/>
-    <mergeCell ref="Q223:Q224"/>
-    <mergeCell ref="A230:A234"/>
-    <mergeCell ref="B230:B234"/>
-    <mergeCell ref="C230:C234"/>
-    <mergeCell ref="D230:D234"/>
-    <mergeCell ref="E230:E234"/>
-    <mergeCell ref="G230:G234"/>
-    <mergeCell ref="H230:H234"/>
-    <mergeCell ref="I230:I234"/>
-    <mergeCell ref="J223:J224"/>
-    <mergeCell ref="K223:K224"/>
-    <mergeCell ref="L223:L224"/>
-    <mergeCell ref="M223:M224"/>
-    <mergeCell ref="N223:N224"/>
-    <mergeCell ref="O223:O224"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="B235:B236"/>
-    <mergeCell ref="C235:C236"/>
-    <mergeCell ref="D235:D236"/>
-    <mergeCell ref="E235:E236"/>
-    <mergeCell ref="G235:G236"/>
-    <mergeCell ref="H235:H236"/>
-    <mergeCell ref="I235:I236"/>
-    <mergeCell ref="J230:J234"/>
-    <mergeCell ref="P235:P236"/>
-    <mergeCell ref="Q235:Q236"/>
-    <mergeCell ref="J235:J236"/>
-    <mergeCell ref="K235:K236"/>
-    <mergeCell ref="L235:L236"/>
-    <mergeCell ref="M235:M236"/>
-    <mergeCell ref="N235:N236"/>
-    <mergeCell ref="O235:O236"/>
-    <mergeCell ref="P230:P234"/>
-    <mergeCell ref="Q230:Q234"/>
-    <mergeCell ref="K230:K234"/>
-    <mergeCell ref="L230:L234"/>
-    <mergeCell ref="M230:M234"/>
-    <mergeCell ref="N230:N234"/>
-    <mergeCell ref="O230:O234"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11463,7 +11466,7 @@
         <v>452</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="57" x14ac:dyDescent="0.45">
@@ -11502,12 +11505,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A5" s="58" t="s">
         <v>454</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="C5" s="61">
         <f>COUNTIF(wiki!R:R,classifications!A5)</f>
@@ -11535,10 +11538,10 @@
         <v>450</v>
       </c>
       <c r="B1" s="64" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C1" s="61" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -11722,7 +11725,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="53" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G1" s="53" t="s">
         <v>6</v>
@@ -11731,7 +11734,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="53" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J1" s="53" t="s">
         <v>9</v>
@@ -11743,13 +11746,13 @@
         <v>11</v>
       </c>
       <c r="M1" s="53" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N1" s="53" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="53" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P1" s="53" t="s">
         <v>15</v>
@@ -11761,10 +11764,10 @@
         <v>450</v>
       </c>
       <c r="S1" s="53" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T1" s="53" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="57" x14ac:dyDescent="0.45">
@@ -11845,7 +11848,7 @@
         <f t="array" ref="S2">_xlfn.LET(_xlpm.txt,LOWER(B2&amp;" "&amp;C2&amp;" "&amp;F2&amp;" "&amp;M2&amp;" "&amp;O2),_xlfn.IFS(IFERROR(SEARCH("diw",_xlpm.txt),0)&gt;0,"diw",IFERROR(SEARCH("cost review",_xlpm.txt),0)&gt;0,"cost review",IFERROR(SEARCH("re-induction",_xlpm.txt),0)&gt;0,"re-induction",IFERROR(SEARCH("second induction",_xlpm.txt),0)&gt;0,"second induction",IFERROR(SEARCH("quotation",_xlpm.txt),0)&gt;0,"quotation",IFERROR(SEARCH("swap",_xlpm.txt),0)&gt;0,"swap",IFERROR(SEARCH("off-module",_xlpm.txt),0)&gt;0,"off-module",IFERROR(SEARCH("off module",_xlpm.txt),0)&gt;0,"off module",IFERROR(SEARCH("dispatch module",_xlpm.txt),0)&gt;0,"dispatch module",IFERROR(SEARCH("notif",_xlpm.txt),0)&gt;0,"notification",IFERROR(SEARCH("line manager",_xlpm.txt),0)&gt;0,"line manager",IFERROR(SEARCH("reject reason",_xlpm.txt),0)&gt;0,"reject reason",IFERROR(SEARCH("approval",_xlpm.txt),0)&gt;0,"approval",IFERROR(SEARCH("approve",_xlpm.txt),0)&gt;0,"approve",IFERROR(SEARCH("calendar",_xlpm.txt),0)&gt;0,"calendar",IFERROR(SEARCH("task owner",_xlpm.txt),0)&gt;0,"task owner",IFERROR(SEARCH("pcd",_xlpm.txt),0)&gt;0,"PCD",IFERROR(SEARCH("acd",_xlpm.txt),0)&gt;0,"ACD",IFERROR(SEARCH("actual completion",_xlpm.txt),0)&gt;0,"actual completion",IFERROR(SEARCH("delay",_xlpm.txt),0)&gt;0,"delay",IFERROR(SEARCH("task ",_xlpm.txt),0)&gt;0,"task",IFERROR(SEARCH("tasks",_xlpm.txt),0)&gt;0,"tasks",TRUE,"(no match)"))</f>
         <v>diw</v>
       </c>
-      <c r="T2" s="54" t="s">
+      <c r="T2" s="89" t="s">
         <v>59</v>
       </c>
     </row>
@@ -12338,7 +12341,7 @@
         <v>approval</v>
       </c>
       <c r="T8" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -12419,7 +12422,7 @@
         <v>notification</v>
       </c>
       <c r="T9" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -12581,7 +12584,7 @@
         <v>notification</v>
       </c>
       <c r="T11" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -12824,7 +12827,7 @@
         <v>notification</v>
       </c>
       <c r="T14" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -12905,7 +12908,7 @@
         <v>reject reason</v>
       </c>
       <c r="T15" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
@@ -12986,7 +12989,7 @@
         <v>notification</v>
       </c>
       <c r="T16" s="54" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -13068,7 +13071,7 @@
         <v>line manager</v>
       </c>
       <c r="T17" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -14692,7 +14695,7 @@
         <v>(no match)</v>
       </c>
       <c r="T37" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -14855,7 +14858,7 @@
         <v>(no match)</v>
       </c>
       <c r="T39" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -14936,7 +14939,7 @@
         <v>(no match)</v>
       </c>
       <c r="T40" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
@@ -15018,7 +15021,7 @@
         <v>(no match)</v>
       </c>
       <c r="T41" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -15181,7 +15184,7 @@
         <v>(no match)</v>
       </c>
       <c r="T43" s="54" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
@@ -15672,7 +15675,7 @@
         <v>(no match)</v>
       </c>
       <c r="T49" s="54" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -15753,7 +15756,7 @@
         <v>(no match)</v>
       </c>
       <c r="T50" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -15834,7 +15837,7 @@
         <v>(no match)</v>
       </c>
       <c r="T51" s="54" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -15915,7 +15918,7 @@
         <v>(no match)</v>
       </c>
       <c r="T52" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -15996,7 +15999,7 @@
         <v>(no match)</v>
       </c>
       <c r="T53" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -17385,7 +17388,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:20" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A71" s="54">
         <f>raw!A8</f>
         <v>6</v>
@@ -17466,7 +17469,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:20" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A72" s="54">
         <f>raw!A78</f>
         <v>56</v>
@@ -17547,7 +17550,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:20" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A73" s="54">
         <f>raw!A89</f>
         <v>61</v>
@@ -17625,11 +17628,11 @@
         <f t="array" ref="S73">_xlfn.LET(_xlpm.txt,LOWER(B73&amp;" "&amp;C73&amp;" "&amp;F73&amp;" "&amp;M73&amp;" "&amp;O73),_xlfn.IFS(IFERROR(SEARCH("diw",_xlpm.txt),0)&gt;0,"diw",IFERROR(SEARCH("cost review",_xlpm.txt),0)&gt;0,"cost review",IFERROR(SEARCH("re-induction",_xlpm.txt),0)&gt;0,"re-induction",IFERROR(SEARCH("second induction",_xlpm.txt),0)&gt;0,"second induction",IFERROR(SEARCH("quotation",_xlpm.txt),0)&gt;0,"quotation",IFERROR(SEARCH("swap",_xlpm.txt),0)&gt;0,"swap",IFERROR(SEARCH("off-module",_xlpm.txt),0)&gt;0,"off-module",IFERROR(SEARCH("off module",_xlpm.txt),0)&gt;0,"off module",IFERROR(SEARCH("dispatch module",_xlpm.txt),0)&gt;0,"dispatch module",IFERROR(SEARCH("notif",_xlpm.txt),0)&gt;0,"notification",IFERROR(SEARCH("line manager",_xlpm.txt),0)&gt;0,"line manager",IFERROR(SEARCH("reject reason",_xlpm.txt),0)&gt;0,"reject reason",IFERROR(SEARCH("approval",_xlpm.txt),0)&gt;0,"approval",IFERROR(SEARCH("approve",_xlpm.txt),0)&gt;0,"approve",IFERROR(SEARCH("calendar",_xlpm.txt),0)&gt;0,"calendar",IFERROR(SEARCH("task owner",_xlpm.txt),0)&gt;0,"task owner",IFERROR(SEARCH("pcd",_xlpm.txt),0)&gt;0,"PCD",IFERROR(SEARCH("acd",_xlpm.txt),0)&gt;0,"ACD",IFERROR(SEARCH("actual completion",_xlpm.txt),0)&gt;0,"actual completion",IFERROR(SEARCH("delay",_xlpm.txt),0)&gt;0,"delay",IFERROR(SEARCH("task ",_xlpm.txt),0)&gt;0,"task",IFERROR(SEARCH("tasks",_xlpm.txt),0)&gt;0,"tasks",TRUE,"(no match)"))</f>
         <v>swap</v>
       </c>
-      <c r="T73" s="54" t="s">
+      <c r="T73" s="89" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:20" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A74" s="54">
         <f>raw!A117</f>
         <v>81</v>
@@ -17710,7 +17713,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:20" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A75" s="54">
         <f>raw!A136</f>
         <v>92</v>
@@ -17795,7 +17798,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:20" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A76" s="54">
         <f>raw!A182</f>
         <v>109</v>
@@ -17876,7 +17879,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:20" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A77" s="54">
         <f>raw!A205</f>
         <v>126</v>
@@ -18603,7 +18606,7 @@
         <v>ACD</v>
       </c>
       <c r="T85" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="86" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -18927,7 +18930,7 @@
         <v>task owner</v>
       </c>
       <c r="T89" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="90" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -19008,7 +19011,7 @@
         <v>task owner</v>
       </c>
       <c r="T90" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="91" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -19089,7 +19092,7 @@
         <v>task</v>
       </c>
       <c r="T91" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="92" spans="1:20" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
@@ -19170,7 +19173,7 @@
         <v>task</v>
       </c>
       <c r="T92" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="93" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -19332,7 +19335,7 @@
         <v>task</v>
       </c>
       <c r="T94" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
@@ -19413,7 +19416,7 @@
         <v>tasks</v>
       </c>
       <c r="T95" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="96" spans="1:20" ht="57" hidden="1" x14ac:dyDescent="0.45">
@@ -19577,7 +19580,7 @@
         <v>actual completion</v>
       </c>
       <c r="T97" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="57" hidden="1" x14ac:dyDescent="0.45">
@@ -19739,7 +19742,7 @@
         <v>tasks</v>
       </c>
       <c r="T99" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -19820,7 +19823,7 @@
         <v>PCD</v>
       </c>
       <c r="T100" s="54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -20067,7 +20070,7 @@
         <v>task</v>
       </c>
       <c r="T103" s="54" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
@@ -21311,7 +21314,7 @@
         <v>task</v>
       </c>
       <c r="T118" s="54" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="119" spans="1:20" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
@@ -21554,7 +21557,7 @@
         <v>task owner</v>
       </c>
       <c r="T121" s="54" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
@@ -23758,6 +23761,7 @@
     <filterColumn colId="17">
       <filters>
         <filter val="DIW/Cost Review"/>
+        <filter val="Swap Module"/>
       </filters>
     </filterColumn>
   </autoFilter>
